--- a/reports/pdf_weekly_20261030.xlsx
+++ b/reports/pdf_weekly_20261030.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,566억   ·   현금 4억(0.1%)      주말 2026-10-30  vs  주초 2026-10-26      매수 5종목  /  매도 8종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,493억      주말 2026-10-30  vs  주초 2026-10-26      매수 5종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>210</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>4435722590</v>
+        <v>4435725178</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-174</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1546225800</v>
+        <v>-1546226702</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>170</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>3996374829</v>
+        <v>3996377161</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-47</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2090629364</v>
+        <v>-2090630584</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>92</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>784623414</v>
+        <v>784623872</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-36</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-844501941</v>
+        <v>-844502434</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>38</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>778102777</v>
+        <v>778103231</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-32</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-927202696</v>
+        <v>-927203237</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1245282523</v>
+        <v>1245283250</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-14</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-858616734</v>
+        <v>-858617235</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>-8</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2071494875</v>
+        <v>-2071496083</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>-4</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-846887540</v>
+        <v>-846888034</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>-4</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-884659519</v>
+        <v>-884660036</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,983억   ·   현금 74억(2.5%)      주말 2026-10-30  vs  주초 2026-10-26      매수 2종목  /  매도 2종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,943억      주말 2026-10-30  vs  주초 2026-10-26      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -1063,7 +1063,7 @@
         <v>36</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1504029544</v>
+        <v>1504029152</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>-24</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-2867579893</v>
+        <v>-2867579146</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>30</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>6258734767</v>
+        <v>6258733135</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>-8</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-5868335781</v>
+        <v>-5868334252</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,229억   ·   현금 36억(1.7%)      주말 2026-10-30  vs  주초 2026-10-26      매수 14종목  /  매도 13종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,154억      주말 2026-10-30  vs  주초 2026-10-26      매수 14종목  /  매도 13종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1240,7 +1240,7 @@
         <v>500</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>9354677805</v>
+        <v>9354679768</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>-700</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-4127397238</v>
+        <v>-4127398104</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>187</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>2192736477</v>
+        <v>2192736938</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>-380</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-8820410645</v>
+        <v>-8820412496</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>124</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>7286576985</v>
+        <v>7286578514</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>-350</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-5521094156</v>
+        <v>-5521095314</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>103</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>1724395617</v>
+        <v>1724395979</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>-240</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-7683842304</v>
+        <v>-7683843917</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>100</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>5716191714</v>
+        <v>5716192914</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>-120</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-5578789673</v>
+        <v>-5578790844</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>79</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>3266966980</v>
+        <v>3266967665</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>-119</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-1192976548</v>
+        <v>-1192976798</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>70</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>2110388633</v>
+        <v>2110389076</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>-101</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-1022631367</v>
+        <v>-1022631581</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>61</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4247724074</v>
+        <v>4247724965</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>-86</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-4078439423</v>
+        <v>-4078440279</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>61</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2982357994</v>
+        <v>2982358620</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>-60</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-1152576346</v>
+        <v>-1152576588</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>50</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>2177755653</v>
+        <v>2177756110</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>-59</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-7642354892</v>
+        <v>-7642356496</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>50</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>2234450670</v>
+        <v>2234451139</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>-50</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-1317325395</v>
+        <v>-1317325672</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>38</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>2445889733</v>
+        <v>2445890247</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>-26</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-1219142966</v>
+        <v>-1219143221</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>6198099358</v>
+        <v>6198100659</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>-20</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-2361180708</v>
+        <v>-2361181204</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>14</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>2054360616</v>
+        <v>2054361047</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,074억   ·   현금 1억(0.1%)      주말 2026-10-30  vs  주초 2026-10-26      매수 4종목  /  매도 2종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,054억      주말 2026-10-30  vs  주초 2026-10-26      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B39" s="4" t="n"/>
@@ -1929,7 +1929,7 @@
         <v>138</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>2249586747</v>
+        <v>2255167953</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>-254</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-3746449944</v>
+        <v>-3755744856</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>87</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1462043990</v>
+        <v>1465671310</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>-44</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-1312168260</v>
+        <v>-1315423740</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>85</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>804992660</v>
+        <v>806989840</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>85</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>1846344867</v>
+        <v>1850925633</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
     <row r="47" ht="19" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 253억   ·   현금 1억(0.6%)      주말 2026-10-30  vs  주초 2026-10-26      매수 3종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 245억      주말 2026-10-30  vs  주초 2026-10-26      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B47" s="4" t="n"/>
@@ -2162,11 +2162,11 @@
         <v>145</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>145603200</v>
+        <v>138643157</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>3.25%→3.82%</t>
+          <t>3.20%→3.76%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2183,11 +2183,11 @@
         <v>-75</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-45216000</v>
+        <v>-42911987</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>1.34%→1.16%</t>
+          <t>1.32%→1.14%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
@@ -2206,11 +2206,11 @@
         <v>61</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>24126720</v>
+        <v>24243832</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>0.29%→0.39%</t>
+          <t>0.30%→0.40%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2227,11 +2227,11 @@
         <v>-67</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-105484800</v>
+        <v>-101411168</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>5.23%→4.79%</t>
+          <t>5.19%→4.76%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -2250,7 +2250,7 @@
         <v>5</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>32960000</v>
+        <v>31679990</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -2271,11 +2271,11 @@
         <v>-4</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-13363200</v>
+        <v>-12287996</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>1.00%→0.94%</t>
+          <t>0.95%→0.90%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2287,7 +2287,7 @@
     <row r="54" ht="19" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 419억   ·   현금 3억(0.6%)      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 1종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 415억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B54" s="4" t="n"/>
@@ -2388,7 +2388,7 @@
         <v>-17</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-366863529</v>
+        <v>-366863657</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,037억   ·   현금 65억(6.3%)      주말 2026-10-30  vs  주초 2026-10-26      매수 2종목  /  매도 1종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,025억      주말 2026-10-30  vs  주초 2026-10-26      매수 2종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B59" s="4" t="n"/>
@@ -2500,7 +2500,7 @@
         <v>8</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>102434356</v>
+        <v>102581902</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>-5</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-777626664</v>
+        <v>-778746753</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>5</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>561098757</v>
+        <v>561906961</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
     <row r="65" ht="19" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 913억   ·   현금 4억(0.4%)      주말 2026-10-30  vs  주초 2026-10-26      매수 7종목  /  매도 10종목</t>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 907억      주말 2026-10-30  vs  주초 2026-10-26      매수 7종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B65" s="4" t="n"/>
@@ -2661,7 +2661,7 @@
         <v>723</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>1221724969</v>
+        <v>1228911733</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>-198</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-1257200556</v>
+        <v>-1264596004</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>292</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>1250927558</v>
+        <v>1258286106</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>-166</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-395079861</v>
+        <v>-397403907</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>152</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>693803755</v>
+        <v>697885037</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>-163</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-1184602082</v>
+        <v>-1191570471</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>120</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>1056719627</v>
+        <v>1062935751</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>-97</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-418845852</v>
+        <v>-421309701</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>92</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>274951103</v>
+        <v>276568495</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>-38</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-163437942</v>
+        <v>-164399362</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>69</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>418174352</v>
+        <v>420634252</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>-20</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-885699687</v>
+        <v>-890909792</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>66</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>463385836</v>
+        <v>466111691</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>-8</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>-310759890</v>
+        <v>-312587927</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>-7</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-254064910</v>
+        <v>-255559440</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>-6</v>
       </c>
       <c r="I76" s="15" t="n">
-        <v>-319769887</v>
+        <v>-321650925</v>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>-4</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>-282199900</v>
+        <v>-283859934</v>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
     <row r="79" ht="19" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 308억   ·   현금 2억(0.6%)      주말 2026-10-30  vs  주초 2026-10-26      매수 11종목  /  매도 14종목</t>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 301억      주말 2026-10-30  vs  주초 2026-10-26      매수 11종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B79" s="4" t="n"/>
@@ -3142,7 +3142,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="11" t="n">
-        <v>452861172</v>
+        <v>452861495</v>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>-127</v>
       </c>
       <c r="I82" s="15" t="n">
-        <v>-392982357</v>
+        <v>-392982637</v>
       </c>
       <c r="J82" s="16" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>55</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>437860946</v>
+        <v>437861258</v>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>-77</v>
       </c>
       <c r="I83" s="15" t="n">
-        <v>-361449464</v>
+        <v>-361449722</v>
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
@@ -3223,23 +3223,23 @@
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>루닛  (신규)</t>
         </is>
       </c>
       <c r="B84" s="11" t="n">
         <v>38</v>
       </c>
       <c r="C84" s="11" t="n">
-        <v>159020082</v>
+        <v>239650154</v>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>2.38%→3.02%</t>
+          <t>0.00%→0.80%</t>
         </is>
       </c>
       <c r="E84" s="13" t="inlineStr">
         <is>
-          <t>178→216</t>
+          <t>0→38</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -3251,7 +3251,7 @@
         <v>-72</v>
       </c>
       <c r="I84" s="15" t="n">
-        <v>-102454536</v>
+        <v>-102454609</v>
       </c>
       <c r="J84" s="16" t="inlineStr">
         <is>
@@ -3267,23 +3267,23 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>루닛  (신규)</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="B85" s="11" t="n">
         <v>38</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>239649983</v>
+        <v>159020196</v>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.80%</t>
+          <t>2.38%→3.02%</t>
         </is>
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>0→38</t>
+          <t>178→216</t>
         </is>
       </c>
       <c r="G85" s="14" t="inlineStr">
@@ -3295,7 +3295,7 @@
         <v>-29</v>
       </c>
       <c r="I85" s="15" t="n">
-        <v>-194367234</v>
+        <v>-194367372</v>
       </c>
       <c r="J85" s="16" t="inlineStr">
         <is>
@@ -3311,23 +3311,23 @@
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>제이에스링크</t>
+          <t>태웅  (신규)</t>
         </is>
       </c>
       <c r="B86" s="11" t="n">
         <v>24</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>193996754</v>
+        <v>238454513</v>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>0.32%→1.00%</t>
+          <t>0.00%→0.80%</t>
         </is>
       </c>
       <c r="E86" s="13" t="inlineStr">
         <is>
-          <t>13→37</t>
+          <t>0→24</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -3339,7 +3339,7 @@
         <v>-26</v>
       </c>
       <c r="I86" s="15" t="n">
-        <v>-339873219</v>
+        <v>-339873461</v>
       </c>
       <c r="J86" s="16" t="inlineStr">
         <is>
@@ -3355,23 +3355,23 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>태웅  (신규)</t>
+          <t>제이에스링크</t>
         </is>
       </c>
       <c r="B87" s="11" t="n">
         <v>24</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>238454343</v>
+        <v>193996892</v>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.80%</t>
+          <t>0.32%→1.00%</t>
         </is>
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>0→24</t>
+          <t>13→37</t>
         </is>
       </c>
       <c r="G87" s="14" t="inlineStr">
@@ -3383,7 +3383,7 @@
         <v>-19</v>
       </c>
       <c r="I87" s="15" t="n">
-        <v>-99667516</v>
+        <v>-99667587</v>
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>11</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>287121932</v>
+        <v>287122136</v>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
@@ -3420,23 +3420,23 @@
       </c>
       <c r="G88" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H88" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I88" s="15" t="n">
-        <v>-231128945</v>
+        <v>-411106695</v>
       </c>
       <c r="J88" s="16" t="inlineStr">
         <is>
-          <t>2.07%→0.72%</t>
+          <t>3.20%→1.56%</t>
         </is>
       </c>
       <c r="K88" s="13" t="inlineStr">
         <is>
-          <t>29→14</t>
+          <t>32→17</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
         <v>7</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>363659714</v>
+        <v>363659973</v>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
@@ -3464,23 +3464,23 @@
       </c>
       <c r="G89" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H89" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I89" s="15" t="n">
-        <v>-411106402</v>
+        <v>-231129110</v>
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>3.20%→1.56%</t>
+          <t>2.07%→0.72%</t>
         </is>
       </c>
       <c r="K89" s="13" t="inlineStr">
         <is>
-          <t>32→17</t>
+          <t>29→14</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
         <v>5</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>83147480</v>
+        <v>83147540</v>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>-11</v>
       </c>
       <c r="I90" s="15" t="n">
-        <v>-90813888</v>
+        <v>-90813953</v>
       </c>
       <c r="J90" s="16" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>4</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>175809558</v>
+        <v>175809684</v>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>-10</v>
       </c>
       <c r="I91" s="15" t="n">
-        <v>-95356477</v>
+        <v>-95356545</v>
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>3</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>47930839</v>
+        <v>47930873</v>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
@@ -3596,23 +3596,23 @@
       </c>
       <c r="G92" s="14" t="inlineStr">
         <is>
-          <t>태성</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H92" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I92" s="15" t="n">
-        <v>-154717463</v>
+        <v>-102555649</v>
       </c>
       <c r="J92" s="16" t="inlineStr">
         <is>
-          <t>1.99%→1.48%</t>
+          <t>0.93%→0.44%</t>
         </is>
       </c>
       <c r="K92" s="13" t="inlineStr">
         <is>
-          <t>27→20</t>
+          <t>16→9</t>
         </is>
       </c>
     </row>
@@ -3624,23 +3624,23 @@
       <c r="E93" s="17" t="n"/>
       <c r="G93" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>태성</t>
         </is>
       </c>
       <c r="H93" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I93" s="15" t="n">
-        <v>-102555576</v>
+        <v>-154717574</v>
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>0.93%→0.44%</t>
+          <t>1.99%→1.48%</t>
         </is>
       </c>
       <c r="K93" s="13" t="inlineStr">
         <is>
-          <t>16→9</t>
+          <t>27→20</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3659,7 @@
         <v>-5</v>
       </c>
       <c r="I94" s="15" t="n">
-        <v>-86304980</v>
+        <v>-86305041</v>
       </c>
       <c r="J94" s="16" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>-3</v>
       </c>
       <c r="I95" s="15" t="n">
-        <v>-121879471</v>
+        <v>-121879558</v>
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
     <row r="97" ht="19" customHeight="1">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>■ SOL 코리아메가테크액티브  (신한)      순자산 ≈ 4,218억   ·   현금 20억(0.5%)      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
+          <t>■ SOL 코리아메가테크액티브  (신한)      순자산 ≈ 4,113억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B97" s="4" t="n"/>
@@ -3727,7 +3727,7 @@
     <row r="100" ht="19" customHeight="1">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,287억   ·   현금 47억(1.4%)      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
+          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,254억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B100" s="4" t="n"/>
@@ -3785,7 +3785,7 @@
     <row r="107" ht="19" customHeight="1">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 827억   ·   현금 6억(0.7%)      주말 2026-10-30  vs  주초 2026-10-26      매수 2종목  /  매도 2종목</t>
+          <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 808억      주말 2026-10-30  vs  주초 2026-10-26      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B107" s="4" t="n"/>
@@ -3962,7 +3962,7 @@
     <row r="113" ht="19" customHeight="1">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct AI인프라액티브  (삼성액티브)      순자산 ≈ 374억   ·   현금 3억(0.8%)      주말 2026-10-30  vs  주초 2026-10-26      매수 11종목  /  매도 11종목</t>
+          <t>■ KoAct AI인프라액티브  (삼성액티브)      순자산 ≈ 366억      주말 2026-10-30  vs  주초 2026-10-26      매수 11종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B113" s="4" t="n"/>
@@ -4535,7 +4535,7 @@
     <row r="128" ht="19" customHeight="1">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 534억   ·   현금 -2억(-0.4%)      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
+          <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 540억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B128" s="4" t="n"/>
@@ -4610,7 +4610,7 @@
     <row r="137" ht="19" customHeight="1">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 287억   ·   현금 2억(0.5%)      주말 2026-10-30  vs  주초 2026-10-26      매수 2종목  /  매도 2종목</t>
+          <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 281억      주말 2026-10-30  vs  주초 2026-10-26      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B137" s="4" t="n"/>
@@ -4706,7 +4706,7 @@
         <v>42</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>54285000</v>
+        <v>55271980</v>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>-95</v>
       </c>
       <c r="I140" s="15" t="n">
-        <v>-134543750</v>
+        <v>-136989951</v>
       </c>
       <c r="J140" s="16" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>32</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>83864000</v>
+        <v>85388770</v>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>-3</v>
       </c>
       <c r="I141" s="15" t="n">
-        <v>-72682500</v>
+        <v>-74003974</v>
       </c>
       <c r="J141" s="16" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
     <row r="143" ht="19" customHeight="1">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 161억   ·   현금 2억(1.0%)      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
+          <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 157억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B143" s="4" t="n"/>
@@ -4811,7 +4811,7 @@
     <row r="146" ht="19" customHeight="1">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 반도체&amp;2차전지핵심소재액티브  (삼성액티브)      순자산 ≈ 89억   ·   현금 3억(3.4%)      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 반도체&amp;2차전지핵심소재액티브  (삼성액티브)      순자산 ≈ 87억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B146" s="4" t="n"/>
@@ -4835,7 +4835,7 @@
     <row r="149" ht="19" customHeight="1">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 59억   ·   현금 1억(1.6%)      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 58억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B149" s="4" t="n"/>

--- a/reports/pdf_weekly_20261030.xlsx
+++ b/reports/pdf_weekly_20261030.xlsx
@@ -59,13 +59,13 @@
       <color rgb="000070C0"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="8">
@@ -171,11 +171,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K150"/>
+  <dimension ref="A1:K149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>주간 변화  ·  2026-10-26 ~ 2026-10-30  (5거래일)  ·  캡처 18/23  ·  대기: TIGER, RISE, RISE, DS, RISE</t>
+          <t>주간 변화  ·  2026-10-26 ~ 2026-10-30  (5거래일)  ·  캡처 17/23  ·  대기: SOL, TIGER, RISE, RISE, DS, RISE</t>
         </is>
       </c>
     </row>
@@ -916,23 +916,23 @@
       <c r="E12" s="17" t="n"/>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-846888034</v>
+        <v>-884660036</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>1.18%→0.94%</t>
+          <t>0.99%→0.69%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>24→20</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
@@ -944,23 +944,23 @@
       <c r="E13" s="17" t="n"/>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-884660036</v>
+        <v>-846888034</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.99%→0.69%</t>
+          <t>1.18%→0.94%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>24→20</t>
         </is>
       </c>
     </row>
@@ -2010,23 +2010,23 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B44" s="11" t="n">
         <v>85</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>806989840</v>
+        <v>1850925633</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>1.16%→1.71%</t>
+          <t>1.02%→2.23%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>285→370</t>
+          <t>125→210</t>
         </is>
       </c>
       <c r="G44" s="17" t="n"/>
@@ -2038,23 +2038,23 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
         <v>85</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>1850925633</v>
+        <v>806989840</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>1.02%→2.23%</t>
+          <t>1.16%→1.71%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>125→210</t>
+          <t>285→370</t>
         </is>
       </c>
       <c r="G45" s="17" t="n"/>
@@ -3596,23 +3596,23 @@
       </c>
       <c r="G92" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>태성</t>
         </is>
       </c>
       <c r="H92" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I92" s="15" t="n">
-        <v>-102555649</v>
+        <v>-154717574</v>
       </c>
       <c r="J92" s="16" t="inlineStr">
         <is>
-          <t>0.93%→0.44%</t>
+          <t>1.99%→1.48%</t>
         </is>
       </c>
       <c r="K92" s="13" t="inlineStr">
         <is>
-          <t>16→9</t>
+          <t>27→20</t>
         </is>
       </c>
     </row>
@@ -3624,23 +3624,23 @@
       <c r="E93" s="17" t="n"/>
       <c r="G93" s="14" t="inlineStr">
         <is>
-          <t>태성</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H93" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I93" s="15" t="n">
-        <v>-154717574</v>
+        <v>-102555649</v>
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>1.99%→1.48%</t>
+          <t>0.93%→0.44%</t>
         </is>
       </c>
       <c r="K93" s="13" t="inlineStr">
         <is>
-          <t>27→20</t>
+          <t>16→9</t>
         </is>
       </c>
     </row>
@@ -3701,1216 +3701,1208 @@
       </c>
     </row>
     <row r="97" ht="19" customHeight="1">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>■ SOL 코리아메가테크액티브  (신한)      순자산 ≈ 4,113억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="n"/>
-      <c r="C97" s="4" t="n"/>
-      <c r="D97" s="4" t="n"/>
-      <c r="E97" s="4" t="n"/>
-      <c r="F97" s="4" t="n"/>
-      <c r="G97" s="4" t="n"/>
-      <c r="H97" s="4" t="n"/>
-      <c r="I97" s="4" t="n"/>
-      <c r="J97" s="4" t="n"/>
-      <c r="K97" s="4" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="18" t="inlineStr">
+      <c r="A97" s="18" t="inlineStr">
+        <is>
+          <t>■ SOL 코리아메가테크액티브  (신한)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B97" s="19" t="n"/>
+      <c r="C97" s="19" t="n"/>
+      <c r="D97" s="19" t="n"/>
+      <c r="E97" s="19" t="n"/>
+      <c r="F97" s="19" t="n"/>
+      <c r="G97" s="19" t="n"/>
+      <c r="H97" s="19" t="n"/>
+      <c r="I97" s="19" t="n"/>
+      <c r="J97" s="19" t="n"/>
+      <c r="K97" s="19" t="n"/>
+    </row>
+    <row r="99" ht="19" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,254억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="n"/>
+      <c r="C99" s="4" t="n"/>
+      <c r="D99" s="4" t="n"/>
+      <c r="E99" s="4" t="n"/>
+      <c r="F99" s="4" t="n"/>
+      <c r="G99" s="4" t="n"/>
+      <c r="H99" s="4" t="n"/>
+      <c r="I99" s="4" t="n"/>
+      <c r="J99" s="4" t="n"/>
+      <c r="K99" s="4" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="19" customHeight="1">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,254억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="n"/>
-      <c r="C100" s="4" t="n"/>
-      <c r="D100" s="4" t="n"/>
-      <c r="E100" s="4" t="n"/>
-      <c r="F100" s="4" t="n"/>
-      <c r="G100" s="4" t="n"/>
-      <c r="H100" s="4" t="n"/>
-      <c r="I100" s="4" t="n"/>
-      <c r="J100" s="4" t="n"/>
-      <c r="K100" s="4" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="18" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="19" customHeight="1">
-      <c r="A103" s="19" t="inlineStr">
+    <row r="102" ht="19" customHeight="1">
+      <c r="A102" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 코리아테크액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B103" s="20" t="n"/>
-      <c r="C103" s="20" t="n"/>
-      <c r="D103" s="20" t="n"/>
-      <c r="E103" s="20" t="n"/>
-      <c r="F103" s="20" t="n"/>
-      <c r="G103" s="20" t="n"/>
-      <c r="H103" s="20" t="n"/>
-      <c r="I103" s="20" t="n"/>
-      <c r="J103" s="20" t="n"/>
-      <c r="K103" s="20" t="n"/>
-    </row>
-    <row r="105" ht="19" customHeight="1">
-      <c r="A105" s="19" t="inlineStr">
+      <c r="B102" s="19" t="n"/>
+      <c r="C102" s="19" t="n"/>
+      <c r="D102" s="19" t="n"/>
+      <c r="E102" s="19" t="n"/>
+      <c r="F102" s="19" t="n"/>
+      <c r="G102" s="19" t="n"/>
+      <c r="H102" s="19" t="n"/>
+      <c r="I102" s="19" t="n"/>
+      <c r="J102" s="19" t="n"/>
+      <c r="K102" s="19" t="n"/>
+    </row>
+    <row r="104" ht="19" customHeight="1">
+      <c r="A104" s="18" t="inlineStr">
         <is>
           <t>■ RISE 비메모리반도체액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B105" s="20" t="n"/>
-      <c r="C105" s="20" t="n"/>
-      <c r="D105" s="20" t="n"/>
-      <c r="E105" s="20" t="n"/>
-      <c r="F105" s="20" t="n"/>
-      <c r="G105" s="20" t="n"/>
-      <c r="H105" s="20" t="n"/>
-      <c r="I105" s="20" t="n"/>
-      <c r="J105" s="20" t="n"/>
-      <c r="K105" s="20" t="n"/>
-    </row>
-    <row r="107" ht="19" customHeight="1">
-      <c r="A107" s="3" t="inlineStr">
+      <c r="B104" s="19" t="n"/>
+      <c r="C104" s="19" t="n"/>
+      <c r="D104" s="19" t="n"/>
+      <c r="E104" s="19" t="n"/>
+      <c r="F104" s="19" t="n"/>
+      <c r="G104" s="19" t="n"/>
+      <c r="H104" s="19" t="n"/>
+      <c r="I104" s="19" t="n"/>
+      <c r="J104" s="19" t="n"/>
+      <c r="K104" s="19" t="n"/>
+    </row>
+    <row r="106" ht="19" customHeight="1">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 808억      주말 2026-10-30  vs  주초 2026-10-26      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
-      <c r="B107" s="4" t="n"/>
-      <c r="C107" s="4" t="n"/>
-      <c r="D107" s="4" t="n"/>
-      <c r="E107" s="4" t="n"/>
-      <c r="F107" s="4" t="n"/>
-      <c r="G107" s="4" t="n"/>
-      <c r="H107" s="4" t="n"/>
-      <c r="I107" s="4" t="n"/>
-      <c r="J107" s="4" t="n"/>
-      <c r="K107" s="4" t="n"/>
+      <c r="B106" s="4" t="n"/>
+      <c r="C106" s="4" t="n"/>
+      <c r="D106" s="4" t="n"/>
+      <c r="E106" s="4" t="n"/>
+      <c r="F106" s="4" t="n"/>
+      <c r="G106" s="4" t="n"/>
+      <c r="H106" s="4" t="n"/>
+      <c r="I106" s="4" t="n"/>
+      <c r="J106" s="4" t="n"/>
+      <c r="K106" s="4" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="n"/>
+      <c r="C107" s="6" t="n"/>
+      <c r="D107" s="6" t="n"/>
+      <c r="E107" s="6" t="n"/>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="n"/>
+      <c r="I107" s="8" t="n"/>
+      <c r="J107" s="8" t="n"/>
+      <c r="K107" s="8" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="n"/>
-      <c r="C108" s="6" t="n"/>
-      <c r="D108" s="6" t="n"/>
-      <c r="E108" s="6" t="n"/>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H108" s="8" t="n"/>
-      <c r="I108" s="8" t="n"/>
-      <c r="J108" s="8" t="n"/>
-      <c r="K108" s="8" t="n"/>
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K108" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C109" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E109" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G109" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H109" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I109" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J109" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K109" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="C109" s="11" t="n">
+        <v>767188000</v>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>4.24%→5.30%</t>
+        </is>
+      </c>
+      <c r="E109" s="13" t="inlineStr">
+        <is>
+          <t>209→255</t>
+        </is>
+      </c>
+      <c r="G109" s="14" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="H109" s="15" t="n">
+        <v>-1215</v>
+      </c>
+      <c r="I109" s="15" t="n">
+        <v>-772132500</v>
+      </c>
+      <c r="J109" s="16" t="inlineStr">
+        <is>
+          <t>2.95%→1.69%</t>
+        </is>
+      </c>
+      <c r="K109" s="13" t="inlineStr">
+        <is>
+          <t>3,349→2,134</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B110" s="11" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>767188000</v>
+        <v>881826000</v>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>4.24%→5.30%</t>
+          <t>2.92%→4.25%</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>209→255</t>
+          <t>63→85</t>
         </is>
       </c>
       <c r="G110" s="14" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="H110" s="15" t="n">
-        <v>-1215</v>
+        <v>-117</v>
       </c>
       <c r="I110" s="15" t="n">
-        <v>-772132500</v>
+        <v>-748975500</v>
       </c>
       <c r="J110" s="16" t="inlineStr">
         <is>
-          <t>2.95%→1.69%</t>
+          <t>1.99%→0.86%</t>
         </is>
       </c>
       <c r="K110" s="13" t="inlineStr">
         <is>
-          <t>3,349→2,134</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="B111" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="C111" s="11" t="n">
-        <v>881826000</v>
-      </c>
-      <c r="D111" s="12" t="inlineStr">
-        <is>
-          <t>2.92%→4.25%</t>
-        </is>
-      </c>
-      <c r="E111" s="13" t="inlineStr">
-        <is>
-          <t>63→85</t>
-        </is>
-      </c>
-      <c r="G111" s="14" t="inlineStr">
-        <is>
-          <t>삼성에스디에스</t>
-        </is>
-      </c>
-      <c r="H111" s="15" t="n">
-        <v>-117</v>
-      </c>
-      <c r="I111" s="15" t="n">
-        <v>-748975500</v>
-      </c>
-      <c r="J111" s="16" t="inlineStr">
-        <is>
-          <t>1.99%→0.86%</t>
-        </is>
-      </c>
-      <c r="K111" s="13" t="inlineStr">
-        <is>
           <t>225→108</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="19" customHeight="1">
-      <c r="A113" s="3" t="inlineStr">
+    <row r="112" ht="19" customHeight="1">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t>■ KoAct AI인프라액티브  (삼성액티브)      순자산 ≈ 366억      주말 2026-10-30  vs  주초 2026-10-26      매수 11종목  /  매도 11종목</t>
         </is>
       </c>
-      <c r="B113" s="4" t="n"/>
-      <c r="C113" s="4" t="n"/>
-      <c r="D113" s="4" t="n"/>
-      <c r="E113" s="4" t="n"/>
-      <c r="F113" s="4" t="n"/>
-      <c r="G113" s="4" t="n"/>
-      <c r="H113" s="4" t="n"/>
-      <c r="I113" s="4" t="n"/>
-      <c r="J113" s="4" t="n"/>
-      <c r="K113" s="4" t="n"/>
+      <c r="B112" s="4" t="n"/>
+      <c r="C112" s="4" t="n"/>
+      <c r="D112" s="4" t="n"/>
+      <c r="E112" s="4" t="n"/>
+      <c r="F112" s="4" t="n"/>
+      <c r="G112" s="4" t="n"/>
+      <c r="H112" s="4" t="n"/>
+      <c r="I112" s="4" t="n"/>
+      <c r="J112" s="4" t="n"/>
+      <c r="K112" s="4" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="n"/>
+      <c r="C113" s="6" t="n"/>
+      <c r="D113" s="6" t="n"/>
+      <c r="E113" s="6" t="n"/>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="n"/>
+      <c r="I113" s="8" t="n"/>
+      <c r="J113" s="8" t="n"/>
+      <c r="K113" s="8" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="n"/>
-      <c r="C114" s="6" t="n"/>
-      <c r="D114" s="6" t="n"/>
-      <c r="E114" s="6" t="n"/>
-      <c r="G114" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H114" s="8" t="n"/>
-      <c r="I114" s="8" t="n"/>
-      <c r="J114" s="8" t="n"/>
-      <c r="K114" s="8" t="n"/>
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G114" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K114" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C115" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D115" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E115" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G115" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H115" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I115" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J115" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K115" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>샘씨엔에스  (신규)</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="n">
+        <v>1174</v>
+      </c>
+      <c r="C115" s="11" t="n">
+        <v>577889760</v>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.59%</t>
+        </is>
+      </c>
+      <c r="E115" s="13" t="inlineStr">
+        <is>
+          <t>0→1,174</t>
+        </is>
+      </c>
+      <c r="G115" s="14" t="inlineStr">
+        <is>
+          <t>파인엠텍  (편출)</t>
+        </is>
+      </c>
+      <c r="H115" s="15" t="n">
+        <v>-1566</v>
+      </c>
+      <c r="I115" s="15" t="n">
+        <v>-488905200</v>
+      </c>
+      <c r="J115" s="16" t="inlineStr">
+        <is>
+          <t>1.43%→0.00%</t>
+        </is>
+      </c>
+      <c r="K115" s="13" t="inlineStr">
+        <is>
+          <t>1,566→0</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>샘씨엔에스  (신규)</t>
+          <t>한화비전  (신규)</t>
         </is>
       </c>
       <c r="B116" s="11" t="n">
-        <v>1174</v>
+        <v>997</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>577889760</v>
+        <v>1370675600</v>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.59%</t>
+          <t>0.00%→3.78%</t>
         </is>
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>0→1,174</t>
+          <t>0→997</t>
         </is>
       </c>
       <c r="G116" s="14" t="inlineStr">
         <is>
-          <t>파인엠텍  (편출)</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-1566</v>
+        <v>-541</v>
       </c>
       <c r="I116" s="15" t="n">
-        <v>-488905200</v>
+        <v>-691506200</v>
       </c>
       <c r="J116" s="16" t="inlineStr">
         <is>
-          <t>1.43%→0.00%</t>
+          <t>3.36%→1.13%</t>
         </is>
       </c>
       <c r="K116" s="13" t="inlineStr">
         <is>
-          <t>1,566→0</t>
+          <t>861→320</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>한화비전  (신규)</t>
+          <t>인텍플러스  (신규)</t>
         </is>
       </c>
       <c r="B117" s="11" t="n">
-        <v>997</v>
+        <v>324</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>1370675600</v>
+        <v>562464000</v>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>0.00%→3.78%</t>
+          <t>0.00%→1.55%</t>
         </is>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>0→997</t>
+          <t>0→324</t>
         </is>
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>두산퓨얼셀  (편출)</t>
         </is>
       </c>
       <c r="H117" s="15" t="n">
-        <v>-541</v>
+        <v>-513</v>
       </c>
       <c r="I117" s="15" t="n">
-        <v>-691506200</v>
+        <v>-453902400</v>
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>3.36%→1.13%</t>
+          <t>1.33%→0.00%</t>
         </is>
       </c>
       <c r="K117" s="13" t="inlineStr">
         <is>
-          <t>861→320</t>
+          <t>513→0</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스  (신규)</t>
+          <t>ISC  (신규)</t>
         </is>
       </c>
       <c r="B118" s="11" t="n">
-        <v>324</v>
+        <v>165</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>562464000</v>
+        <v>767844000</v>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.55%</t>
+          <t>0.00%→2.12%</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>0→324</t>
+          <t>0→165</t>
         </is>
       </c>
       <c r="G118" s="14" t="inlineStr">
         <is>
-          <t>두산퓨얼셀  (편출)</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="H118" s="15" t="n">
-        <v>-513</v>
+        <v>-473</v>
       </c>
       <c r="I118" s="15" t="n">
-        <v>-453902400</v>
+        <v>-750934800</v>
       </c>
       <c r="J118" s="16" t="inlineStr">
         <is>
-          <t>1.33%→0.00%</t>
+          <t>2.86%→0.50%</t>
         </is>
       </c>
       <c r="K118" s="13" t="inlineStr">
         <is>
-          <t>513→0</t>
+          <t>588→115</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>ISC  (신규)</t>
+          <t>에코프로에이치엔  (신규)</t>
         </is>
       </c>
       <c r="B119" s="11" t="n">
-        <v>165</v>
+        <v>111</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>767844000</v>
+        <v>73038000</v>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.12%</t>
+          <t>0.00%→0.20%</t>
         </is>
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>0→165</t>
+          <t>0→111</t>
         </is>
       </c>
       <c r="G119" s="14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>솔루엠  (편출)</t>
         </is>
       </c>
       <c r="H119" s="15" t="n">
-        <v>-473</v>
+        <v>-325</v>
       </c>
       <c r="I119" s="15" t="n">
-        <v>-750934800</v>
+        <v>-132496000</v>
       </c>
       <c r="J119" s="16" t="inlineStr">
         <is>
-          <t>2.86%→0.50%</t>
+          <t>0.39%→0.00%</t>
         </is>
       </c>
       <c r="K119" s="13" t="inlineStr">
         <is>
-          <t>588→115</t>
+          <t>325→0</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>에코프로에이치엔  (신규)</t>
+          <t>케이씨텍</t>
         </is>
       </c>
       <c r="B120" s="11" t="n">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>73038000</v>
+        <v>163800000</v>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.20%</t>
+          <t>4.99%→5.29%</t>
         </is>
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>0→111</t>
+          <t>644→704</t>
         </is>
       </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
-          <t>솔루엠  (편출)</t>
+          <t>현대건설  (편출)</t>
         </is>
       </c>
       <c r="H120" s="15" t="n">
-        <v>-325</v>
+        <v>-216</v>
       </c>
       <c r="I120" s="15" t="n">
-        <v>-132496000</v>
+        <v>-559440000</v>
       </c>
       <c r="J120" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.00%</t>
+          <t>1.64%→0.00%</t>
         </is>
       </c>
       <c r="K120" s="13" t="inlineStr">
         <is>
-          <t>325→0</t>
+          <t>216→0</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>케이씨텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B121" s="11" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>163800000</v>
+        <v>168565600</v>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>4.99%→5.29%</t>
+          <t>5.55%→6.32%</t>
         </is>
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>644→704</t>
+          <t>391→422</t>
         </is>
       </c>
       <c r="G121" s="14" t="inlineStr">
         <is>
-          <t>현대건설  (편출)</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="H121" s="15" t="n">
-        <v>-216</v>
+        <v>-138</v>
       </c>
       <c r="I121" s="15" t="n">
-        <v>-559440000</v>
+        <v>-896448000</v>
       </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
-          <t>1.64%→0.00%</t>
+          <t>8.61%→6.26%</t>
         </is>
       </c>
       <c r="K121" s="13" t="inlineStr">
         <is>
-          <t>216→0</t>
+          <t>488→350</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B122" s="11" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>168565600</v>
+        <v>118431600</v>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>5.55%→6.32%</t>
+          <t>5.28%→5.77%</t>
         </is>
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>391→422</t>
+          <t>384→407</t>
         </is>
       </c>
       <c r="G122" s="14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="H122" s="15" t="n">
-        <v>-138</v>
+        <v>-30</v>
       </c>
       <c r="I122" s="15" t="n">
-        <v>-896448000</v>
+        <v>-299040000</v>
       </c>
       <c r="J122" s="16" t="inlineStr">
         <is>
-          <t>8.61%→6.26%</t>
+          <t>4.14%→2.80%</t>
         </is>
       </c>
       <c r="K122" s="13" t="inlineStr">
         <is>
-          <t>488→350</t>
+          <t>132→102</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B123" s="11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>118431600</v>
+        <v>331408000</v>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>5.28%→5.77%</t>
+          <t>5.38%→6.47%</t>
         </is>
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>384→407</t>
+          <t>134→156</t>
         </is>
       </c>
       <c r="G123" s="14" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="H123" s="15" t="n">
-        <v>-30</v>
+        <v>-24</v>
       </c>
       <c r="I123" s="15" t="n">
-        <v>-299040000</v>
+        <v>-18480000</v>
       </c>
       <c r="J123" s="16" t="inlineStr">
         <is>
-          <t>4.14%→2.80%</t>
+          <t>2.94%→2.77%</t>
         </is>
       </c>
       <c r="K123" s="13" t="inlineStr">
         <is>
-          <t>132→102</t>
+          <t>1,328→1,304</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B124" s="11" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>331408000</v>
+        <v>341824000</v>
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>5.38%→6.47%</t>
+          <t>8.68%→10.71%</t>
         </is>
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>134→156</t>
+          <t>83→91</t>
         </is>
       </c>
       <c r="G124" s="14" t="inlineStr">
         <is>
-          <t>에스티아이</t>
+          <t>HD현대일렉트릭  (편출)</t>
         </is>
       </c>
       <c r="H124" s="15" t="n">
-        <v>-24</v>
+        <v>-8</v>
       </c>
       <c r="I124" s="15" t="n">
-        <v>-18480000</v>
+        <v>-105280000</v>
       </c>
       <c r="J124" s="16" t="inlineStr">
         <is>
-          <t>2.94%→2.77%</t>
+          <t>0.31%→0.00%</t>
         </is>
       </c>
       <c r="K124" s="13" t="inlineStr">
         <is>
-          <t>1,328→1,304</t>
+          <t>8→0</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B125" s="11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C125" s="11" t="n">
-        <v>341824000</v>
+        <v>108612000</v>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>8.68%→10.71%</t>
+          <t>1.10%→1.50%</t>
         </is>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>83→91</t>
+          <t>12→15</t>
         </is>
       </c>
       <c r="G125" s="14" t="inlineStr">
         <is>
-          <t>HD현대일렉트릭  (편출)</t>
+          <t>두산  (편출)</t>
         </is>
       </c>
       <c r="H125" s="15" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="I125" s="15" t="n">
-        <v>-105280000</v>
+        <v>-188944000</v>
       </c>
       <c r="J125" s="16" t="inlineStr">
         <is>
-          <t>0.31%→0.00%</t>
+          <t>0.55%→0.00%</t>
         </is>
       </c>
       <c r="K125" s="13" t="inlineStr">
         <is>
-          <t>8→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="10" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="B126" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C126" s="11" t="n">
-        <v>108612000</v>
-      </c>
-      <c r="D126" s="12" t="inlineStr">
-        <is>
-          <t>1.10%→1.50%</t>
-        </is>
-      </c>
-      <c r="E126" s="13" t="inlineStr">
-        <is>
-          <t>12→15</t>
-        </is>
-      </c>
-      <c r="G126" s="14" t="inlineStr">
-        <is>
-          <t>두산  (편출)</t>
-        </is>
-      </c>
-      <c r="H126" s="15" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I126" s="15" t="n">
-        <v>-188944000</v>
-      </c>
-      <c r="J126" s="16" t="inlineStr">
-        <is>
-          <t>0.55%→0.00%</t>
-        </is>
-      </c>
-      <c r="K126" s="13" t="inlineStr">
-        <is>
           <t>7→0</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="19" customHeight="1">
-      <c r="A128" s="3" t="inlineStr">
+    <row r="127" ht="19" customHeight="1">
+      <c r="A127" s="3" t="inlineStr">
         <is>
           <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 540억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B128" s="4" t="n"/>
-      <c r="C128" s="4" t="n"/>
-      <c r="D128" s="4" t="n"/>
-      <c r="E128" s="4" t="n"/>
-      <c r="F128" s="4" t="n"/>
-      <c r="G128" s="4" t="n"/>
-      <c r="H128" s="4" t="n"/>
-      <c r="I128" s="4" t="n"/>
-      <c r="J128" s="4" t="n"/>
-      <c r="K128" s="4" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="18" t="inlineStr">
+      <c r="B127" s="4" t="n"/>
+      <c r="C127" s="4" t="n"/>
+      <c r="D127" s="4" t="n"/>
+      <c r="E127" s="4" t="n"/>
+      <c r="F127" s="4" t="n"/>
+      <c r="G127" s="4" t="n"/>
+      <c r="H127" s="4" t="n"/>
+      <c r="I127" s="4" t="n"/>
+      <c r="J127" s="4" t="n"/>
+      <c r="K127" s="4" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="19" customHeight="1">
-      <c r="A131" s="19" t="inlineStr">
+    <row r="130" ht="19" customHeight="1">
+      <c r="A130" s="18" t="inlineStr">
         <is>
           <t>■ RISE 반도체소부장액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B131" s="20" t="n"/>
-      <c r="C131" s="20" t="n"/>
-      <c r="D131" s="20" t="n"/>
-      <c r="E131" s="20" t="n"/>
-      <c r="F131" s="20" t="n"/>
-      <c r="G131" s="20" t="n"/>
-      <c r="H131" s="20" t="n"/>
-      <c r="I131" s="20" t="n"/>
-      <c r="J131" s="20" t="n"/>
-      <c r="K131" s="20" t="n"/>
-    </row>
-    <row r="133" ht="19" customHeight="1">
-      <c r="A133" s="19" t="inlineStr">
+      <c r="B130" s="19" t="n"/>
+      <c r="C130" s="19" t="n"/>
+      <c r="D130" s="19" t="n"/>
+      <c r="E130" s="19" t="n"/>
+      <c r="F130" s="19" t="n"/>
+      <c r="G130" s="19" t="n"/>
+      <c r="H130" s="19" t="n"/>
+      <c r="I130" s="19" t="n"/>
+      <c r="J130" s="19" t="n"/>
+      <c r="K130" s="19" t="n"/>
+    </row>
+    <row r="132" ht="19" customHeight="1">
+      <c r="A132" s="18" t="inlineStr">
         <is>
           <t>■ DS AI반도체액티브  (DS)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B133" s="20" t="n"/>
-      <c r="C133" s="20" t="n"/>
-      <c r="D133" s="20" t="n"/>
-      <c r="E133" s="20" t="n"/>
-      <c r="F133" s="20" t="n"/>
-      <c r="G133" s="20" t="n"/>
-      <c r="H133" s="20" t="n"/>
-      <c r="I133" s="20" t="n"/>
-      <c r="J133" s="20" t="n"/>
-      <c r="K133" s="20" t="n"/>
-    </row>
-    <row r="135" ht="19" customHeight="1">
-      <c r="A135" s="19" t="inlineStr">
+      <c r="B132" s="19" t="n"/>
+      <c r="C132" s="19" t="n"/>
+      <c r="D132" s="19" t="n"/>
+      <c r="E132" s="19" t="n"/>
+      <c r="F132" s="19" t="n"/>
+      <c r="G132" s="19" t="n"/>
+      <c r="H132" s="19" t="n"/>
+      <c r="I132" s="19" t="n"/>
+      <c r="J132" s="19" t="n"/>
+      <c r="K132" s="19" t="n"/>
+    </row>
+    <row r="134" ht="19" customHeight="1">
+      <c r="A134" s="18" t="inlineStr">
         <is>
           <t>■ RISE 2차전지액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B135" s="20" t="n"/>
-      <c r="C135" s="20" t="n"/>
-      <c r="D135" s="20" t="n"/>
-      <c r="E135" s="20" t="n"/>
-      <c r="F135" s="20" t="n"/>
-      <c r="G135" s="20" t="n"/>
-      <c r="H135" s="20" t="n"/>
-      <c r="I135" s="20" t="n"/>
-      <c r="J135" s="20" t="n"/>
-      <c r="K135" s="20" t="n"/>
-    </row>
-    <row r="137" ht="19" customHeight="1">
-      <c r="A137" s="3" t="inlineStr">
+      <c r="B134" s="19" t="n"/>
+      <c r="C134" s="19" t="n"/>
+      <c r="D134" s="19" t="n"/>
+      <c r="E134" s="19" t="n"/>
+      <c r="F134" s="19" t="n"/>
+      <c r="G134" s="19" t="n"/>
+      <c r="H134" s="19" t="n"/>
+      <c r="I134" s="19" t="n"/>
+      <c r="J134" s="19" t="n"/>
+      <c r="K134" s="19" t="n"/>
+    </row>
+    <row r="136" ht="19" customHeight="1">
+      <c r="A136" s="3" t="inlineStr">
         <is>
           <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 281억      주말 2026-10-30  vs  주초 2026-10-26      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
-      <c r="B137" s="4" t="n"/>
-      <c r="C137" s="4" t="n"/>
-      <c r="D137" s="4" t="n"/>
-      <c r="E137" s="4" t="n"/>
-      <c r="F137" s="4" t="n"/>
-      <c r="G137" s="4" t="n"/>
-      <c r="H137" s="4" t="n"/>
-      <c r="I137" s="4" t="n"/>
-      <c r="J137" s="4" t="n"/>
-      <c r="K137" s="4" t="n"/>
+      <c r="B136" s="4" t="n"/>
+      <c r="C136" s="4" t="n"/>
+      <c r="D136" s="4" t="n"/>
+      <c r="E136" s="4" t="n"/>
+      <c r="F136" s="4" t="n"/>
+      <c r="G136" s="4" t="n"/>
+      <c r="H136" s="4" t="n"/>
+      <c r="I136" s="4" t="n"/>
+      <c r="J136" s="4" t="n"/>
+      <c r="K136" s="4" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="n"/>
+      <c r="C137" s="6" t="n"/>
+      <c r="D137" s="6" t="n"/>
+      <c r="E137" s="6" t="n"/>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H137" s="8" t="n"/>
+      <c r="I137" s="8" t="n"/>
+      <c r="J137" s="8" t="n"/>
+      <c r="K137" s="8" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="n"/>
-      <c r="C138" s="6" t="n"/>
-      <c r="D138" s="6" t="n"/>
-      <c r="E138" s="6" t="n"/>
-      <c r="G138" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H138" s="8" t="n"/>
-      <c r="I138" s="8" t="n"/>
-      <c r="J138" s="8" t="n"/>
-      <c r="K138" s="8" t="n"/>
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G138" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H138" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K138" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B139" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C139" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D139" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E139" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G139" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H139" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I139" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J139" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K139" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A139" s="10" t="inlineStr">
+        <is>
+          <t>에코프로에이치엔</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="C139" s="11" t="n">
+        <v>55271980</v>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>0.50%→0.73%</t>
+        </is>
+      </c>
+      <c r="E139" s="13" t="inlineStr">
+        <is>
+          <t>112→154</t>
+        </is>
+      </c>
+      <c r="G139" s="14" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="H139" s="15" t="n">
+        <v>-95</v>
+      </c>
+      <c r="I139" s="15" t="n">
+        <v>-136989951</v>
+      </c>
+      <c r="J139" s="16" t="inlineStr">
+        <is>
+          <t>8.72%→9.20%</t>
+        </is>
+      </c>
+      <c r="K139" s="13" t="inlineStr">
+        <is>
+          <t>1,876→1,781</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>에코프로에이치엔</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="B140" s="11" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>55271980</v>
+        <v>85388770</v>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>0.50%→0.73%</t>
+          <t>6.65%→7.49%</t>
         </is>
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>112→154</t>
+          <t>752→784</t>
         </is>
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>HD현대일렉트릭</t>
         </is>
       </c>
       <c r="H140" s="15" t="n">
-        <v>-95</v>
+        <v>-3</v>
       </c>
       <c r="I140" s="15" t="n">
-        <v>-136989951</v>
+        <v>-74003974</v>
       </c>
       <c r="J140" s="16" t="inlineStr">
         <is>
-          <t>8.72%→9.20%</t>
+          <t>2.17%→1.85%</t>
         </is>
       </c>
       <c r="K140" s="13" t="inlineStr">
         <is>
-          <t>1,876→1,781</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="10" t="inlineStr">
-        <is>
-          <t>한중엔시에스</t>
-        </is>
-      </c>
-      <c r="B141" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="C141" s="11" t="n">
-        <v>85388770</v>
-      </c>
-      <c r="D141" s="12" t="inlineStr">
-        <is>
-          <t>6.65%→7.49%</t>
-        </is>
-      </c>
-      <c r="E141" s="13" t="inlineStr">
-        <is>
-          <t>752→784</t>
-        </is>
-      </c>
-      <c r="G141" s="14" t="inlineStr">
-        <is>
-          <t>HD현대일렉트릭</t>
-        </is>
-      </c>
-      <c r="H141" s="15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I141" s="15" t="n">
-        <v>-74003974</v>
-      </c>
-      <c r="J141" s="16" t="inlineStr">
-        <is>
-          <t>2.17%→1.85%</t>
-        </is>
-      </c>
-      <c r="K141" s="13" t="inlineStr">
-        <is>
           <t>24→21</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="19" customHeight="1">
-      <c r="A143" s="3" t="inlineStr">
+    <row r="142" ht="19" customHeight="1">
+      <c r="A142" s="3" t="inlineStr">
         <is>
           <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 157억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B143" s="4" t="n"/>
-      <c r="C143" s="4" t="n"/>
-      <c r="D143" s="4" t="n"/>
-      <c r="E143" s="4" t="n"/>
-      <c r="F143" s="4" t="n"/>
-      <c r="G143" s="4" t="n"/>
-      <c r="H143" s="4" t="n"/>
-      <c r="I143" s="4" t="n"/>
-      <c r="J143" s="4" t="n"/>
-      <c r="K143" s="4" t="n"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="18" t="inlineStr">
+      <c r="B142" s="4" t="n"/>
+      <c r="C142" s="4" t="n"/>
+      <c r="D142" s="4" t="n"/>
+      <c r="E142" s="4" t="n"/>
+      <c r="F142" s="4" t="n"/>
+      <c r="G142" s="4" t="n"/>
+      <c r="H142" s="4" t="n"/>
+      <c r="I142" s="4" t="n"/>
+      <c r="J142" s="4" t="n"/>
+      <c r="K142" s="4" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="19" customHeight="1">
-      <c r="A146" s="3" t="inlineStr">
+    <row r="145" ht="19" customHeight="1">
+      <c r="A145" s="3" t="inlineStr">
         <is>
           <t>■ KoAct 반도체&amp;2차전지핵심소재액티브  (삼성액티브)      순자산 ≈ 87억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B146" s="4" t="n"/>
-      <c r="C146" s="4" t="n"/>
-      <c r="D146" s="4" t="n"/>
-      <c r="E146" s="4" t="n"/>
-      <c r="F146" s="4" t="n"/>
-      <c r="G146" s="4" t="n"/>
-      <c r="H146" s="4" t="n"/>
-      <c r="I146" s="4" t="n"/>
-      <c r="J146" s="4" t="n"/>
-      <c r="K146" s="4" t="n"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="18" t="inlineStr">
+      <c r="B145" s="4" t="n"/>
+      <c r="C145" s="4" t="n"/>
+      <c r="D145" s="4" t="n"/>
+      <c r="E145" s="4" t="n"/>
+      <c r="F145" s="4" t="n"/>
+      <c r="G145" s="4" t="n"/>
+      <c r="H145" s="4" t="n"/>
+      <c r="I145" s="4" t="n"/>
+      <c r="J145" s="4" t="n"/>
+      <c r="K145" s="4" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="19" customHeight="1">
-      <c r="A149" s="3" t="inlineStr">
+    <row r="148" ht="19" customHeight="1">
+      <c r="A148" s="3" t="inlineStr">
         <is>
           <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 58억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B149" s="4" t="n"/>
-      <c r="C149" s="4" t="n"/>
-      <c r="D149" s="4" t="n"/>
-      <c r="E149" s="4" t="n"/>
-      <c r="F149" s="4" t="n"/>
-      <c r="G149" s="4" t="n"/>
-      <c r="H149" s="4" t="n"/>
-      <c r="I149" s="4" t="n"/>
-      <c r="J149" s="4" t="n"/>
-      <c r="K149" s="4" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="18" t="inlineStr">
+      <c r="B148" s="4" t="n"/>
+      <c r="C148" s="4" t="n"/>
+      <c r="D148" s="4" t="n"/>
+      <c r="E148" s="4" t="n"/>
+      <c r="F148" s="4" t="n"/>
+      <c r="G148" s="4" t="n"/>
+      <c r="H148" s="4" t="n"/>
+      <c r="I148" s="4" t="n"/>
+      <c r="J148" s="4" t="n"/>
+      <c r="K148" s="4" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="55">
-    <mergeCell ref="A114:E114"/>
+  <mergeCells count="54">
+    <mergeCell ref="A127:K127"/>
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A143:K143"/>
+    <mergeCell ref="A130:K130"/>
     <mergeCell ref="A39:K39"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A59:K59"/>
     <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A138:E138"/>
-    <mergeCell ref="A107:K107"/>
-    <mergeCell ref="A98:K98"/>
+    <mergeCell ref="A148:K148"/>
+    <mergeCell ref="A142:K142"/>
+    <mergeCell ref="A107:E107"/>
     <mergeCell ref="G22:K22"/>
+    <mergeCell ref="G107:K107"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A103:K103"/>
+    <mergeCell ref="A132:K132"/>
     <mergeCell ref="A79:K79"/>
     <mergeCell ref="G48:K48"/>
     <mergeCell ref="A146:K146"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A54:K54"/>
     <mergeCell ref="A65:K65"/>
-    <mergeCell ref="A108:E108"/>
     <mergeCell ref="A128:K128"/>
     <mergeCell ref="G66:K66"/>
-    <mergeCell ref="A137:K137"/>
-    <mergeCell ref="A133:K133"/>
+    <mergeCell ref="A137:E137"/>
+    <mergeCell ref="A99:K99"/>
     <mergeCell ref="A66:E66"/>
     <mergeCell ref="A80:E80"/>
+    <mergeCell ref="G137:K137"/>
+    <mergeCell ref="A136:K136"/>
     <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A105:K105"/>
     <mergeCell ref="A149:K149"/>
+    <mergeCell ref="A145:K145"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A101:K101"/>
-    <mergeCell ref="G108:K108"/>
-    <mergeCell ref="A113:K113"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A104:K104"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A129:K129"/>
     <mergeCell ref="A47:K47"/>
     <mergeCell ref="G80:K80"/>
-    <mergeCell ref="G114:K114"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="G55:K55"/>
-    <mergeCell ref="A150:K150"/>
     <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A144:K144"/>
+    <mergeCell ref="A106:K106"/>
     <mergeCell ref="A97:K97"/>
-    <mergeCell ref="A135:K135"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A131:K131"/>
     <mergeCell ref="A100:K100"/>
-    <mergeCell ref="G138:K138"/>
-    <mergeCell ref="A147:K147"/>
+    <mergeCell ref="G113:K113"/>
     <mergeCell ref="G60:K60"/>
+    <mergeCell ref="A134:K134"/>
     <mergeCell ref="G16:K16"/>
+    <mergeCell ref="A112:K112"/>
+    <mergeCell ref="A102:K102"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="G40:K40"/>
   </mergeCells>

--- a/reports/pdf_weekly_20261030.xlsx
+++ b/reports/pdf_weekly_20261030.xlsx
@@ -59,13 +59,13 @@
       <color rgb="000070C0"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="8">
@@ -171,11 +171,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K149"/>
+  <dimension ref="A1:K150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>주간 변화  ·  2026-10-26 ~ 2026-10-30  (5거래일)  ·  캡처 17/23  ·  대기: SOL, TIGER, RISE, RISE, DS, RISE</t>
+          <t>주간 변화  ·  2026-10-26 ~ 2026-10-30  (5거래일)  ·  캡처 18/23  ·  대기: TIGER, RISE, RISE, DS, RISE</t>
         </is>
       </c>
     </row>
@@ -2010,23 +2010,23 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B44" s="11" t="n">
         <v>85</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1850925633</v>
+        <v>806989840</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>1.02%→2.23%</t>
+          <t>1.16%→1.71%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>125→210</t>
+          <t>285→370</t>
         </is>
       </c>
       <c r="G44" s="17" t="n"/>
@@ -2038,23 +2038,23 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
         <v>85</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>806989840</v>
+        <v>1850925633</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>1.16%→1.71%</t>
+          <t>1.02%→2.23%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>285→370</t>
+          <t>125→210</t>
         </is>
       </c>
       <c r="G45" s="17" t="n"/>
@@ -3223,23 +3223,23 @@
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>루닛  (신규)</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="B84" s="11" t="n">
         <v>38</v>
       </c>
       <c r="C84" s="11" t="n">
-        <v>239650154</v>
+        <v>159020196</v>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.80%</t>
+          <t>2.38%→3.02%</t>
         </is>
       </c>
       <c r="E84" s="13" t="inlineStr">
         <is>
-          <t>0→38</t>
+          <t>178→216</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -3267,23 +3267,23 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>루닛  (신규)</t>
         </is>
       </c>
       <c r="B85" s="11" t="n">
         <v>38</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>159020196</v>
+        <v>239650154</v>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>2.38%→3.02%</t>
+          <t>0.00%→0.80%</t>
         </is>
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>178→216</t>
+          <t>0→38</t>
         </is>
       </c>
       <c r="G85" s="14" t="inlineStr">
@@ -3420,23 +3420,23 @@
       </c>
       <c r="G88" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H88" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I88" s="15" t="n">
-        <v>-411106695</v>
+        <v>-231129110</v>
       </c>
       <c r="J88" s="16" t="inlineStr">
         <is>
-          <t>3.20%→1.56%</t>
+          <t>2.07%→0.72%</t>
         </is>
       </c>
       <c r="K88" s="13" t="inlineStr">
         <is>
-          <t>32→17</t>
+          <t>29→14</t>
         </is>
       </c>
     </row>
@@ -3464,23 +3464,23 @@
       </c>
       <c r="G89" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H89" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I89" s="15" t="n">
-        <v>-231129110</v>
+        <v>-411106695</v>
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>2.07%→0.72%</t>
+          <t>3.20%→1.56%</t>
         </is>
       </c>
       <c r="K89" s="13" t="inlineStr">
         <is>
-          <t>29→14</t>
+          <t>32→17</t>
         </is>
       </c>
     </row>
@@ -3596,23 +3596,23 @@
       </c>
       <c r="G92" s="14" t="inlineStr">
         <is>
-          <t>태성</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H92" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I92" s="15" t="n">
-        <v>-154717574</v>
+        <v>-102555649</v>
       </c>
       <c r="J92" s="16" t="inlineStr">
         <is>
-          <t>1.99%→1.48%</t>
+          <t>0.93%→0.44%</t>
         </is>
       </c>
       <c r="K92" s="13" t="inlineStr">
         <is>
-          <t>27→20</t>
+          <t>16→9</t>
         </is>
       </c>
     </row>
@@ -3624,23 +3624,23 @@
       <c r="E93" s="17" t="n"/>
       <c r="G93" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>태성</t>
         </is>
       </c>
       <c r="H93" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I93" s="15" t="n">
-        <v>-102555649</v>
+        <v>-154717574</v>
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>0.93%→0.44%</t>
+          <t>1.99%→1.48%</t>
         </is>
       </c>
       <c r="K93" s="13" t="inlineStr">
         <is>
-          <t>16→9</t>
+          <t>27→20</t>
         </is>
       </c>
     </row>
@@ -3701,1208 +3701,1216 @@
       </c>
     </row>
     <row r="97" ht="19" customHeight="1">
-      <c r="A97" s="18" t="inlineStr">
-        <is>
-          <t>■ SOL 코리아메가테크액티브  (신한)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B97" s="19" t="n"/>
-      <c r="C97" s="19" t="n"/>
-      <c r="D97" s="19" t="n"/>
-      <c r="E97" s="19" t="n"/>
-      <c r="F97" s="19" t="n"/>
-      <c r="G97" s="19" t="n"/>
-      <c r="H97" s="19" t="n"/>
-      <c r="I97" s="19" t="n"/>
-      <c r="J97" s="19" t="n"/>
-      <c r="K97" s="19" t="n"/>
-    </row>
-    <row r="99" ht="19" customHeight="1">
-      <c r="A99" s="3" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>■ SOL 코리아메가테크액티브  (신한)      순자산 ≈ 4,113억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="n"/>
+      <c r="C97" s="4" t="n"/>
+      <c r="D97" s="4" t="n"/>
+      <c r="E97" s="4" t="n"/>
+      <c r="F97" s="4" t="n"/>
+      <c r="G97" s="4" t="n"/>
+      <c r="H97" s="4" t="n"/>
+      <c r="I97" s="4" t="n"/>
+      <c r="J97" s="4" t="n"/>
+      <c r="K97" s="4" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="19" customHeight="1">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,254억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B99" s="4" t="n"/>
-      <c r="C99" s="4" t="n"/>
-      <c r="D99" s="4" t="n"/>
-      <c r="E99" s="4" t="n"/>
-      <c r="F99" s="4" t="n"/>
-      <c r="G99" s="4" t="n"/>
-      <c r="H99" s="4" t="n"/>
-      <c r="I99" s="4" t="n"/>
-      <c r="J99" s="4" t="n"/>
-      <c r="K99" s="4" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="20" t="inlineStr">
+      <c r="B100" s="4" t="n"/>
+      <c r="C100" s="4" t="n"/>
+      <c r="D100" s="4" t="n"/>
+      <c r="E100" s="4" t="n"/>
+      <c r="F100" s="4" t="n"/>
+      <c r="G100" s="4" t="n"/>
+      <c r="H100" s="4" t="n"/>
+      <c r="I100" s="4" t="n"/>
+      <c r="J100" s="4" t="n"/>
+      <c r="K100" s="4" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="19" customHeight="1">
-      <c r="A102" s="18" t="inlineStr">
+    <row r="103" ht="19" customHeight="1">
+      <c r="A103" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 코리아테크액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B102" s="19" t="n"/>
-      <c r="C102" s="19" t="n"/>
-      <c r="D102" s="19" t="n"/>
-      <c r="E102" s="19" t="n"/>
-      <c r="F102" s="19" t="n"/>
-      <c r="G102" s="19" t="n"/>
-      <c r="H102" s="19" t="n"/>
-      <c r="I102" s="19" t="n"/>
-      <c r="J102" s="19" t="n"/>
-      <c r="K102" s="19" t="n"/>
-    </row>
-    <row r="104" ht="19" customHeight="1">
-      <c r="A104" s="18" t="inlineStr">
+      <c r="B103" s="20" t="n"/>
+      <c r="C103" s="20" t="n"/>
+      <c r="D103" s="20" t="n"/>
+      <c r="E103" s="20" t="n"/>
+      <c r="F103" s="20" t="n"/>
+      <c r="G103" s="20" t="n"/>
+      <c r="H103" s="20" t="n"/>
+      <c r="I103" s="20" t="n"/>
+      <c r="J103" s="20" t="n"/>
+      <c r="K103" s="20" t="n"/>
+    </row>
+    <row r="105" ht="19" customHeight="1">
+      <c r="A105" s="19" t="inlineStr">
         <is>
           <t>■ RISE 비메모리반도체액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B104" s="19" t="n"/>
-      <c r="C104" s="19" t="n"/>
-      <c r="D104" s="19" t="n"/>
-      <c r="E104" s="19" t="n"/>
-      <c r="F104" s="19" t="n"/>
-      <c r="G104" s="19" t="n"/>
-      <c r="H104" s="19" t="n"/>
-      <c r="I104" s="19" t="n"/>
-      <c r="J104" s="19" t="n"/>
-      <c r="K104" s="19" t="n"/>
-    </row>
-    <row r="106" ht="19" customHeight="1">
-      <c r="A106" s="3" t="inlineStr">
+      <c r="B105" s="20" t="n"/>
+      <c r="C105" s="20" t="n"/>
+      <c r="D105" s="20" t="n"/>
+      <c r="E105" s="20" t="n"/>
+      <c r="F105" s="20" t="n"/>
+      <c r="G105" s="20" t="n"/>
+      <c r="H105" s="20" t="n"/>
+      <c r="I105" s="20" t="n"/>
+      <c r="J105" s="20" t="n"/>
+      <c r="K105" s="20" t="n"/>
+    </row>
+    <row r="107" ht="19" customHeight="1">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 808억      주말 2026-10-30  vs  주초 2026-10-26      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
-      <c r="B106" s="4" t="n"/>
-      <c r="C106" s="4" t="n"/>
-      <c r="D106" s="4" t="n"/>
-      <c r="E106" s="4" t="n"/>
-      <c r="F106" s="4" t="n"/>
-      <c r="G106" s="4" t="n"/>
-      <c r="H106" s="4" t="n"/>
-      <c r="I106" s="4" t="n"/>
-      <c r="J106" s="4" t="n"/>
-      <c r="K106" s="4" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
+      <c r="B107" s="4" t="n"/>
+      <c r="C107" s="4" t="n"/>
+      <c r="D107" s="4" t="n"/>
+      <c r="E107" s="4" t="n"/>
+      <c r="F107" s="4" t="n"/>
+      <c r="G107" s="4" t="n"/>
+      <c r="H107" s="4" t="n"/>
+      <c r="I107" s="4" t="n"/>
+      <c r="J107" s="4" t="n"/>
+      <c r="K107" s="4" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B107" s="6" t="n"/>
-      <c r="C107" s="6" t="n"/>
-      <c r="D107" s="6" t="n"/>
-      <c r="E107" s="6" t="n"/>
-      <c r="G107" s="7" t="inlineStr">
+      <c r="B108" s="6" t="n"/>
+      <c r="C108" s="6" t="n"/>
+      <c r="D108" s="6" t="n"/>
+      <c r="E108" s="6" t="n"/>
+      <c r="G108" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H107" s="8" t="n"/>
-      <c r="I107" s="8" t="n"/>
-      <c r="J107" s="8" t="n"/>
-      <c r="K107" s="8" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="9" t="inlineStr">
+      <c r="H108" s="8" t="n"/>
+      <c r="I108" s="8" t="n"/>
+      <c r="J108" s="8" t="n"/>
+      <c r="K108" s="8" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B108" s="9" t="inlineStr">
+      <c r="B109" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C108" s="9" t="inlineStr">
+      <c r="C109" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D108" s="9" t="inlineStr">
+      <c r="D109" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E108" s="9" t="inlineStr">
+      <c r="E109" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G108" s="9" t="inlineStr">
+      <c r="G109" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H108" s="9" t="inlineStr">
+      <c r="H109" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I108" s="9" t="inlineStr">
+      <c r="I109" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J108" s="9" t="inlineStr">
+      <c r="J109" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K108" s="9" t="inlineStr">
+      <c r="K109" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="10" t="inlineStr">
-        <is>
-          <t>삼성SDI</t>
-        </is>
-      </c>
-      <c r="B109" s="11" t="n">
-        <v>46</v>
-      </c>
-      <c r="C109" s="11" t="n">
-        <v>767188000</v>
-      </c>
-      <c r="D109" s="12" t="inlineStr">
-        <is>
-          <t>4.24%→5.30%</t>
-        </is>
-      </c>
-      <c r="E109" s="13" t="inlineStr">
-        <is>
-          <t>209→255</t>
-        </is>
-      </c>
-      <c r="G109" s="14" t="inlineStr">
-        <is>
-          <t>대한전선</t>
-        </is>
-      </c>
-      <c r="H109" s="15" t="n">
-        <v>-1215</v>
-      </c>
-      <c r="I109" s="15" t="n">
-        <v>-772132500</v>
-      </c>
-      <c r="J109" s="16" t="inlineStr">
-        <is>
-          <t>2.95%→1.69%</t>
-        </is>
-      </c>
-      <c r="K109" s="13" t="inlineStr">
-        <is>
-          <t>3,349→2,134</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="C110" s="11" t="n">
+        <v>767188000</v>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>4.24%→5.30%</t>
+        </is>
+      </c>
+      <c r="E110" s="13" t="inlineStr">
+        <is>
+          <t>209→255</t>
+        </is>
+      </c>
+      <c r="G110" s="14" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="H110" s="15" t="n">
+        <v>-1215</v>
+      </c>
+      <c r="I110" s="15" t="n">
+        <v>-772132500</v>
+      </c>
+      <c r="J110" s="16" t="inlineStr">
+        <is>
+          <t>2.95%→1.69%</t>
+        </is>
+      </c>
+      <c r="K110" s="13" t="inlineStr">
+        <is>
+          <t>3,349→2,134</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="B110" s="11" t="n">
+      <c r="B111" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="C110" s="11" t="n">
+      <c r="C111" s="11" t="n">
         <v>881826000</v>
       </c>
-      <c r="D110" s="12" t="inlineStr">
+      <c r="D111" s="12" t="inlineStr">
         <is>
           <t>2.92%→4.25%</t>
         </is>
       </c>
-      <c r="E110" s="13" t="inlineStr">
+      <c r="E111" s="13" t="inlineStr">
         <is>
           <t>63→85</t>
         </is>
       </c>
-      <c r="G110" s="14" t="inlineStr">
+      <c r="G111" s="14" t="inlineStr">
         <is>
           <t>삼성에스디에스</t>
         </is>
       </c>
-      <c r="H110" s="15" t="n">
+      <c r="H111" s="15" t="n">
         <v>-117</v>
       </c>
-      <c r="I110" s="15" t="n">
+      <c r="I111" s="15" t="n">
         <v>-748975500</v>
       </c>
-      <c r="J110" s="16" t="inlineStr">
+      <c r="J111" s="16" t="inlineStr">
         <is>
           <t>1.99%→0.86%</t>
         </is>
       </c>
-      <c r="K110" s="13" t="inlineStr">
+      <c r="K111" s="13" t="inlineStr">
         <is>
           <t>225→108</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="19" customHeight="1">
-      <c r="A112" s="3" t="inlineStr">
+    <row r="113" ht="19" customHeight="1">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>■ KoAct AI인프라액티브  (삼성액티브)      순자산 ≈ 366억      주말 2026-10-30  vs  주초 2026-10-26      매수 11종목  /  매도 11종목</t>
         </is>
       </c>
-      <c r="B112" s="4" t="n"/>
-      <c r="C112" s="4" t="n"/>
-      <c r="D112" s="4" t="n"/>
-      <c r="E112" s="4" t="n"/>
-      <c r="F112" s="4" t="n"/>
-      <c r="G112" s="4" t="n"/>
-      <c r="H112" s="4" t="n"/>
-      <c r="I112" s="4" t="n"/>
-      <c r="J112" s="4" t="n"/>
-      <c r="K112" s="4" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr">
+      <c r="B113" s="4" t="n"/>
+      <c r="C113" s="4" t="n"/>
+      <c r="D113" s="4" t="n"/>
+      <c r="E113" s="4" t="n"/>
+      <c r="F113" s="4" t="n"/>
+      <c r="G113" s="4" t="n"/>
+      <c r="H113" s="4" t="n"/>
+      <c r="I113" s="4" t="n"/>
+      <c r="J113" s="4" t="n"/>
+      <c r="K113" s="4" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B113" s="6" t="n"/>
-      <c r="C113" s="6" t="n"/>
-      <c r="D113" s="6" t="n"/>
-      <c r="E113" s="6" t="n"/>
-      <c r="G113" s="7" t="inlineStr">
+      <c r="B114" s="6" t="n"/>
+      <c r="C114" s="6" t="n"/>
+      <c r="D114" s="6" t="n"/>
+      <c r="E114" s="6" t="n"/>
+      <c r="G114" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H113" s="8" t="n"/>
-      <c r="I113" s="8" t="n"/>
-      <c r="J113" s="8" t="n"/>
-      <c r="K113" s="8" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="9" t="inlineStr">
+      <c r="H114" s="8" t="n"/>
+      <c r="I114" s="8" t="n"/>
+      <c r="J114" s="8" t="n"/>
+      <c r="K114" s="8" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B114" s="9" t="inlineStr">
+      <c r="B115" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C114" s="9" t="inlineStr">
+      <c r="C115" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D114" s="9" t="inlineStr">
+      <c r="D115" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E114" s="9" t="inlineStr">
+      <c r="E115" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G114" s="9" t="inlineStr">
+      <c r="G115" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H114" s="9" t="inlineStr">
+      <c r="H115" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I114" s="9" t="inlineStr">
+      <c r="I115" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J114" s="9" t="inlineStr">
+      <c r="J115" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K114" s="9" t="inlineStr">
+      <c r="K115" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="10" t="inlineStr">
-        <is>
-          <t>샘씨엔에스  (신규)</t>
-        </is>
-      </c>
-      <c r="B115" s="11" t="n">
-        <v>1174</v>
-      </c>
-      <c r="C115" s="11" t="n">
-        <v>577889760</v>
-      </c>
-      <c r="D115" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→1.59%</t>
-        </is>
-      </c>
-      <c r="E115" s="13" t="inlineStr">
-        <is>
-          <t>0→1,174</t>
-        </is>
-      </c>
-      <c r="G115" s="14" t="inlineStr">
-        <is>
-          <t>파인엠텍  (편출)</t>
-        </is>
-      </c>
-      <c r="H115" s="15" t="n">
-        <v>-1566</v>
-      </c>
-      <c r="I115" s="15" t="n">
-        <v>-488905200</v>
-      </c>
-      <c r="J115" s="16" t="inlineStr">
-        <is>
-          <t>1.43%→0.00%</t>
-        </is>
-      </c>
-      <c r="K115" s="13" t="inlineStr">
-        <is>
-          <t>1,566→0</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>한화비전  (신규)</t>
+          <t>샘씨엔에스  (신규)</t>
         </is>
       </c>
       <c r="B116" s="11" t="n">
-        <v>997</v>
+        <v>1174</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>1370675600</v>
+        <v>577889760</v>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>0.00%→3.78%</t>
+          <t>0.00%→1.59%</t>
         </is>
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>0→997</t>
+          <t>0→1,174</t>
         </is>
       </c>
       <c r="G116" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>파인엠텍  (편출)</t>
         </is>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-541</v>
+        <v>-1566</v>
       </c>
       <c r="I116" s="15" t="n">
-        <v>-691506200</v>
+        <v>-488905200</v>
       </c>
       <c r="J116" s="16" t="inlineStr">
         <is>
-          <t>3.36%→1.13%</t>
+          <t>1.43%→0.00%</t>
         </is>
       </c>
       <c r="K116" s="13" t="inlineStr">
         <is>
-          <t>861→320</t>
+          <t>1,566→0</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스  (신규)</t>
+          <t>한화비전  (신규)</t>
         </is>
       </c>
       <c r="B117" s="11" t="n">
-        <v>324</v>
+        <v>997</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>562464000</v>
+        <v>1370675600</v>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.55%</t>
+          <t>0.00%→3.78%</t>
         </is>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>0→324</t>
+          <t>0→997</t>
         </is>
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
-          <t>두산퓨얼셀  (편출)</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H117" s="15" t="n">
-        <v>-513</v>
+        <v>-541</v>
       </c>
       <c r="I117" s="15" t="n">
-        <v>-453902400</v>
+        <v>-691506200</v>
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>1.33%→0.00%</t>
+          <t>3.36%→1.13%</t>
         </is>
       </c>
       <c r="K117" s="13" t="inlineStr">
         <is>
-          <t>513→0</t>
+          <t>861→320</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>ISC  (신규)</t>
+          <t>인텍플러스  (신규)</t>
         </is>
       </c>
       <c r="B118" s="11" t="n">
-        <v>165</v>
+        <v>324</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>767844000</v>
+        <v>562464000</v>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.12%</t>
+          <t>0.00%→1.55%</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>0→165</t>
+          <t>0→324</t>
         </is>
       </c>
       <c r="G118" s="14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>두산퓨얼셀  (편출)</t>
         </is>
       </c>
       <c r="H118" s="15" t="n">
-        <v>-473</v>
+        <v>-513</v>
       </c>
       <c r="I118" s="15" t="n">
-        <v>-750934800</v>
+        <v>-453902400</v>
       </c>
       <c r="J118" s="16" t="inlineStr">
         <is>
-          <t>2.86%→0.50%</t>
+          <t>1.33%→0.00%</t>
         </is>
       </c>
       <c r="K118" s="13" t="inlineStr">
         <is>
-          <t>588→115</t>
+          <t>513→0</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>에코프로에이치엔  (신규)</t>
+          <t>ISC  (신규)</t>
         </is>
       </c>
       <c r="B119" s="11" t="n">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>73038000</v>
+        <v>767844000</v>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.20%</t>
+          <t>0.00%→2.12%</t>
         </is>
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>0→111</t>
+          <t>0→165</t>
         </is>
       </c>
       <c r="G119" s="14" t="inlineStr">
         <is>
-          <t>솔루엠  (편출)</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="H119" s="15" t="n">
-        <v>-325</v>
+        <v>-473</v>
       </c>
       <c r="I119" s="15" t="n">
-        <v>-132496000</v>
+        <v>-750934800</v>
       </c>
       <c r="J119" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.00%</t>
+          <t>2.86%→0.50%</t>
         </is>
       </c>
       <c r="K119" s="13" t="inlineStr">
         <is>
-          <t>325→0</t>
+          <t>588→115</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>케이씨텍</t>
+          <t>에코프로에이치엔  (신규)</t>
         </is>
       </c>
       <c r="B120" s="11" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>163800000</v>
+        <v>73038000</v>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>4.99%→5.29%</t>
+          <t>0.00%→0.20%</t>
         </is>
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>644→704</t>
+          <t>0→111</t>
         </is>
       </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
-          <t>현대건설  (편출)</t>
+          <t>솔루엠  (편출)</t>
         </is>
       </c>
       <c r="H120" s="15" t="n">
-        <v>-216</v>
+        <v>-325</v>
       </c>
       <c r="I120" s="15" t="n">
-        <v>-559440000</v>
+        <v>-132496000</v>
       </c>
       <c r="J120" s="16" t="inlineStr">
         <is>
-          <t>1.64%→0.00%</t>
+          <t>0.39%→0.00%</t>
         </is>
       </c>
       <c r="K120" s="13" t="inlineStr">
         <is>
-          <t>216→0</t>
+          <t>325→0</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>케이씨텍</t>
         </is>
       </c>
       <c r="B121" s="11" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>168565600</v>
+        <v>163800000</v>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>5.55%→6.32%</t>
+          <t>4.99%→5.29%</t>
         </is>
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>391→422</t>
+          <t>644→704</t>
         </is>
       </c>
       <c r="G121" s="14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대건설  (편출)</t>
         </is>
       </c>
       <c r="H121" s="15" t="n">
-        <v>-138</v>
+        <v>-216</v>
       </c>
       <c r="I121" s="15" t="n">
-        <v>-896448000</v>
+        <v>-559440000</v>
       </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
-          <t>8.61%→6.26%</t>
+          <t>1.64%→0.00%</t>
         </is>
       </c>
       <c r="K121" s="13" t="inlineStr">
         <is>
-          <t>488→350</t>
+          <t>216→0</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B122" s="11" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>118431600</v>
+        <v>168565600</v>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>5.28%→5.77%</t>
+          <t>5.55%→6.32%</t>
         </is>
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>384→407</t>
+          <t>391→422</t>
         </is>
       </c>
       <c r="G122" s="14" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="H122" s="15" t="n">
-        <v>-30</v>
+        <v>-138</v>
       </c>
       <c r="I122" s="15" t="n">
-        <v>-299040000</v>
+        <v>-896448000</v>
       </c>
       <c r="J122" s="16" t="inlineStr">
         <is>
-          <t>4.14%→2.80%</t>
+          <t>8.61%→6.26%</t>
         </is>
       </c>
       <c r="K122" s="13" t="inlineStr">
         <is>
-          <t>132→102</t>
+          <t>488→350</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B123" s="11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>331408000</v>
+        <v>118431600</v>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>5.38%→6.47%</t>
+          <t>5.28%→5.77%</t>
         </is>
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>134→156</t>
+          <t>384→407</t>
         </is>
       </c>
       <c r="G123" s="14" t="inlineStr">
         <is>
-          <t>에스티아이</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="H123" s="15" t="n">
-        <v>-24</v>
+        <v>-30</v>
       </c>
       <c r="I123" s="15" t="n">
-        <v>-18480000</v>
+        <v>-299040000</v>
       </c>
       <c r="J123" s="16" t="inlineStr">
         <is>
-          <t>2.94%→2.77%</t>
+          <t>4.14%→2.80%</t>
         </is>
       </c>
       <c r="K123" s="13" t="inlineStr">
         <is>
-          <t>1,328→1,304</t>
+          <t>132→102</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B124" s="11" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>341824000</v>
+        <v>331408000</v>
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>8.68%→10.71%</t>
+          <t>5.38%→6.47%</t>
         </is>
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>83→91</t>
+          <t>134→156</t>
         </is>
       </c>
       <c r="G124" s="14" t="inlineStr">
         <is>
-          <t>HD현대일렉트릭  (편출)</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="H124" s="15" t="n">
-        <v>-8</v>
+        <v>-24</v>
       </c>
       <c r="I124" s="15" t="n">
-        <v>-105280000</v>
+        <v>-18480000</v>
       </c>
       <c r="J124" s="16" t="inlineStr">
         <is>
-          <t>0.31%→0.00%</t>
+          <t>2.94%→2.77%</t>
         </is>
       </c>
       <c r="K124" s="13" t="inlineStr">
         <is>
-          <t>8→0</t>
+          <t>1,328→1,304</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C125" s="11" t="n">
+        <v>341824000</v>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>8.68%→10.71%</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="inlineStr">
+        <is>
+          <t>83→91</t>
+        </is>
+      </c>
+      <c r="G125" s="14" t="inlineStr">
+        <is>
+          <t>HD현대일렉트릭  (편출)</t>
+        </is>
+      </c>
+      <c r="H125" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I125" s="15" t="n">
+        <v>-105280000</v>
+      </c>
+      <c r="J125" s="16" t="inlineStr">
+        <is>
+          <t>0.31%→0.00%</t>
+        </is>
+      </c>
+      <c r="K125" s="13" t="inlineStr">
+        <is>
+          <t>8→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="B125" s="11" t="n">
+      <c r="B126" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C125" s="11" t="n">
+      <c r="C126" s="11" t="n">
         <v>108612000</v>
       </c>
-      <c r="D125" s="12" t="inlineStr">
+      <c r="D126" s="12" t="inlineStr">
         <is>
           <t>1.10%→1.50%</t>
         </is>
       </c>
-      <c r="E125" s="13" t="inlineStr">
+      <c r="E126" s="13" t="inlineStr">
         <is>
           <t>12→15</t>
         </is>
       </c>
-      <c r="G125" s="14" t="inlineStr">
+      <c r="G126" s="14" t="inlineStr">
         <is>
           <t>두산  (편출)</t>
         </is>
       </c>
-      <c r="H125" s="15" t="n">
+      <c r="H126" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I125" s="15" t="n">
+      <c r="I126" s="15" t="n">
         <v>-188944000</v>
       </c>
-      <c r="J125" s="16" t="inlineStr">
+      <c r="J126" s="16" t="inlineStr">
         <is>
           <t>0.55%→0.00%</t>
         </is>
       </c>
-      <c r="K125" s="13" t="inlineStr">
+      <c r="K126" s="13" t="inlineStr">
         <is>
           <t>7→0</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="19" customHeight="1">
-      <c r="A127" s="3" t="inlineStr">
+    <row r="128" ht="19" customHeight="1">
+      <c r="A128" s="3" t="inlineStr">
         <is>
           <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 540억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B127" s="4" t="n"/>
-      <c r="C127" s="4" t="n"/>
-      <c r="D127" s="4" t="n"/>
-      <c r="E127" s="4" t="n"/>
-      <c r="F127" s="4" t="n"/>
-      <c r="G127" s="4" t="n"/>
-      <c r="H127" s="4" t="n"/>
-      <c r="I127" s="4" t="n"/>
-      <c r="J127" s="4" t="n"/>
-      <c r="K127" s="4" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="20" t="inlineStr">
+      <c r="B128" s="4" t="n"/>
+      <c r="C128" s="4" t="n"/>
+      <c r="D128" s="4" t="n"/>
+      <c r="E128" s="4" t="n"/>
+      <c r="F128" s="4" t="n"/>
+      <c r="G128" s="4" t="n"/>
+      <c r="H128" s="4" t="n"/>
+      <c r="I128" s="4" t="n"/>
+      <c r="J128" s="4" t="n"/>
+      <c r="K128" s="4" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="19" customHeight="1">
-      <c r="A130" s="18" t="inlineStr">
+    <row r="131" ht="19" customHeight="1">
+      <c r="A131" s="19" t="inlineStr">
         <is>
           <t>■ RISE 반도체소부장액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B130" s="19" t="n"/>
-      <c r="C130" s="19" t="n"/>
-      <c r="D130" s="19" t="n"/>
-      <c r="E130" s="19" t="n"/>
-      <c r="F130" s="19" t="n"/>
-      <c r="G130" s="19" t="n"/>
-      <c r="H130" s="19" t="n"/>
-      <c r="I130" s="19" t="n"/>
-      <c r="J130" s="19" t="n"/>
-      <c r="K130" s="19" t="n"/>
-    </row>
-    <row r="132" ht="19" customHeight="1">
-      <c r="A132" s="18" t="inlineStr">
+      <c r="B131" s="20" t="n"/>
+      <c r="C131" s="20" t="n"/>
+      <c r="D131" s="20" t="n"/>
+      <c r="E131" s="20" t="n"/>
+      <c r="F131" s="20" t="n"/>
+      <c r="G131" s="20" t="n"/>
+      <c r="H131" s="20" t="n"/>
+      <c r="I131" s="20" t="n"/>
+      <c r="J131" s="20" t="n"/>
+      <c r="K131" s="20" t="n"/>
+    </row>
+    <row r="133" ht="19" customHeight="1">
+      <c r="A133" s="19" t="inlineStr">
         <is>
           <t>■ DS AI반도체액티브  (DS)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B132" s="19" t="n"/>
-      <c r="C132" s="19" t="n"/>
-      <c r="D132" s="19" t="n"/>
-      <c r="E132" s="19" t="n"/>
-      <c r="F132" s="19" t="n"/>
-      <c r="G132" s="19" t="n"/>
-      <c r="H132" s="19" t="n"/>
-      <c r="I132" s="19" t="n"/>
-      <c r="J132" s="19" t="n"/>
-      <c r="K132" s="19" t="n"/>
-    </row>
-    <row r="134" ht="19" customHeight="1">
-      <c r="A134" s="18" t="inlineStr">
+      <c r="B133" s="20" t="n"/>
+      <c r="C133" s="20" t="n"/>
+      <c r="D133" s="20" t="n"/>
+      <c r="E133" s="20" t="n"/>
+      <c r="F133" s="20" t="n"/>
+      <c r="G133" s="20" t="n"/>
+      <c r="H133" s="20" t="n"/>
+      <c r="I133" s="20" t="n"/>
+      <c r="J133" s="20" t="n"/>
+      <c r="K133" s="20" t="n"/>
+    </row>
+    <row r="135" ht="19" customHeight="1">
+      <c r="A135" s="19" t="inlineStr">
         <is>
           <t>■ RISE 2차전지액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B134" s="19" t="n"/>
-      <c r="C134" s="19" t="n"/>
-      <c r="D134" s="19" t="n"/>
-      <c r="E134" s="19" t="n"/>
-      <c r="F134" s="19" t="n"/>
-      <c r="G134" s="19" t="n"/>
-      <c r="H134" s="19" t="n"/>
-      <c r="I134" s="19" t="n"/>
-      <c r="J134" s="19" t="n"/>
-      <c r="K134" s="19" t="n"/>
-    </row>
-    <row r="136" ht="19" customHeight="1">
-      <c r="A136" s="3" t="inlineStr">
+      <c r="B135" s="20" t="n"/>
+      <c r="C135" s="20" t="n"/>
+      <c r="D135" s="20" t="n"/>
+      <c r="E135" s="20" t="n"/>
+      <c r="F135" s="20" t="n"/>
+      <c r="G135" s="20" t="n"/>
+      <c r="H135" s="20" t="n"/>
+      <c r="I135" s="20" t="n"/>
+      <c r="J135" s="20" t="n"/>
+      <c r="K135" s="20" t="n"/>
+    </row>
+    <row r="137" ht="19" customHeight="1">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 281억      주말 2026-10-30  vs  주초 2026-10-26      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
-      <c r="B136" s="4" t="n"/>
-      <c r="C136" s="4" t="n"/>
-      <c r="D136" s="4" t="n"/>
-      <c r="E136" s="4" t="n"/>
-      <c r="F136" s="4" t="n"/>
-      <c r="G136" s="4" t="n"/>
-      <c r="H136" s="4" t="n"/>
-      <c r="I136" s="4" t="n"/>
-      <c r="J136" s="4" t="n"/>
-      <c r="K136" s="4" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="5" t="inlineStr">
+      <c r="B137" s="4" t="n"/>
+      <c r="C137" s="4" t="n"/>
+      <c r="D137" s="4" t="n"/>
+      <c r="E137" s="4" t="n"/>
+      <c r="F137" s="4" t="n"/>
+      <c r="G137" s="4" t="n"/>
+      <c r="H137" s="4" t="n"/>
+      <c r="I137" s="4" t="n"/>
+      <c r="J137" s="4" t="n"/>
+      <c r="K137" s="4" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B137" s="6" t="n"/>
-      <c r="C137" s="6" t="n"/>
-      <c r="D137" s="6" t="n"/>
-      <c r="E137" s="6" t="n"/>
-      <c r="G137" s="7" t="inlineStr">
+      <c r="B138" s="6" t="n"/>
+      <c r="C138" s="6" t="n"/>
+      <c r="D138" s="6" t="n"/>
+      <c r="E138" s="6" t="n"/>
+      <c r="G138" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H137" s="8" t="n"/>
-      <c r="I137" s="8" t="n"/>
-      <c r="J137" s="8" t="n"/>
-      <c r="K137" s="8" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="9" t="inlineStr">
+      <c r="H138" s="8" t="n"/>
+      <c r="I138" s="8" t="n"/>
+      <c r="J138" s="8" t="n"/>
+      <c r="K138" s="8" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B138" s="9" t="inlineStr">
+      <c r="B139" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C138" s="9" t="inlineStr">
+      <c r="C139" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D138" s="9" t="inlineStr">
+      <c r="D139" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E138" s="9" t="inlineStr">
+      <c r="E139" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G138" s="9" t="inlineStr">
+      <c r="G139" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H138" s="9" t="inlineStr">
+      <c r="H139" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I138" s="9" t="inlineStr">
+      <c r="I139" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J138" s="9" t="inlineStr">
+      <c r="J139" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K138" s="9" t="inlineStr">
+      <c r="K139" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="10" t="inlineStr">
-        <is>
-          <t>에코프로에이치엔</t>
-        </is>
-      </c>
-      <c r="B139" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="C139" s="11" t="n">
-        <v>55271980</v>
-      </c>
-      <c r="D139" s="12" t="inlineStr">
-        <is>
-          <t>0.50%→0.73%</t>
-        </is>
-      </c>
-      <c r="E139" s="13" t="inlineStr">
-        <is>
-          <t>112→154</t>
-        </is>
-      </c>
-      <c r="G139" s="14" t="inlineStr">
-        <is>
-          <t>상신이디피</t>
-        </is>
-      </c>
-      <c r="H139" s="15" t="n">
-        <v>-95</v>
-      </c>
-      <c r="I139" s="15" t="n">
-        <v>-136989951</v>
-      </c>
-      <c r="J139" s="16" t="inlineStr">
-        <is>
-          <t>8.72%→9.20%</t>
-        </is>
-      </c>
-      <c r="K139" s="13" t="inlineStr">
-        <is>
-          <t>1,876→1,781</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
+          <t>에코프로에이치엔</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="C140" s="11" t="n">
+        <v>55271980</v>
+      </c>
+      <c r="D140" s="12" t="inlineStr">
+        <is>
+          <t>0.50%→0.73%</t>
+        </is>
+      </c>
+      <c r="E140" s="13" t="inlineStr">
+        <is>
+          <t>112→154</t>
+        </is>
+      </c>
+      <c r="G140" s="14" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="H140" s="15" t="n">
+        <v>-95</v>
+      </c>
+      <c r="I140" s="15" t="n">
+        <v>-136989951</v>
+      </c>
+      <c r="J140" s="16" t="inlineStr">
+        <is>
+          <t>8.72%→9.20%</t>
+        </is>
+      </c>
+      <c r="K140" s="13" t="inlineStr">
+        <is>
+          <t>1,876→1,781</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="inlineStr">
+        <is>
           <t>한중엔시에스</t>
         </is>
       </c>
-      <c r="B140" s="11" t="n">
+      <c r="B141" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="C140" s="11" t="n">
+      <c r="C141" s="11" t="n">
         <v>85388770</v>
       </c>
-      <c r="D140" s="12" t="inlineStr">
+      <c r="D141" s="12" t="inlineStr">
         <is>
           <t>6.65%→7.49%</t>
         </is>
       </c>
-      <c r="E140" s="13" t="inlineStr">
+      <c r="E141" s="13" t="inlineStr">
         <is>
           <t>752→784</t>
         </is>
       </c>
-      <c r="G140" s="14" t="inlineStr">
+      <c r="G141" s="14" t="inlineStr">
         <is>
           <t>HD현대일렉트릭</t>
         </is>
       </c>
-      <c r="H140" s="15" t="n">
+      <c r="H141" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I140" s="15" t="n">
+      <c r="I141" s="15" t="n">
         <v>-74003974</v>
       </c>
-      <c r="J140" s="16" t="inlineStr">
+      <c r="J141" s="16" t="inlineStr">
         <is>
           <t>2.17%→1.85%</t>
         </is>
       </c>
-      <c r="K140" s="13" t="inlineStr">
+      <c r="K141" s="13" t="inlineStr">
         <is>
           <t>24→21</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="19" customHeight="1">
-      <c r="A142" s="3" t="inlineStr">
+    <row r="143" ht="19" customHeight="1">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 157억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B142" s="4" t="n"/>
-      <c r="C142" s="4" t="n"/>
-      <c r="D142" s="4" t="n"/>
-      <c r="E142" s="4" t="n"/>
-      <c r="F142" s="4" t="n"/>
-      <c r="G142" s="4" t="n"/>
-      <c r="H142" s="4" t="n"/>
-      <c r="I142" s="4" t="n"/>
-      <c r="J142" s="4" t="n"/>
-      <c r="K142" s="4" t="n"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="20" t="inlineStr">
+      <c r="B143" s="4" t="n"/>
+      <c r="C143" s="4" t="n"/>
+      <c r="D143" s="4" t="n"/>
+      <c r="E143" s="4" t="n"/>
+      <c r="F143" s="4" t="n"/>
+      <c r="G143" s="4" t="n"/>
+      <c r="H143" s="4" t="n"/>
+      <c r="I143" s="4" t="n"/>
+      <c r="J143" s="4" t="n"/>
+      <c r="K143" s="4" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="19" customHeight="1">
-      <c r="A145" s="3" t="inlineStr">
+    <row r="146" ht="19" customHeight="1">
+      <c r="A146" s="3" t="inlineStr">
         <is>
           <t>■ KoAct 반도체&amp;2차전지핵심소재액티브  (삼성액티브)      순자산 ≈ 87억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B145" s="4" t="n"/>
-      <c r="C145" s="4" t="n"/>
-      <c r="D145" s="4" t="n"/>
-      <c r="E145" s="4" t="n"/>
-      <c r="F145" s="4" t="n"/>
-      <c r="G145" s="4" t="n"/>
-      <c r="H145" s="4" t="n"/>
-      <c r="I145" s="4" t="n"/>
-      <c r="J145" s="4" t="n"/>
-      <c r="K145" s="4" t="n"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="20" t="inlineStr">
+      <c r="B146" s="4" t="n"/>
+      <c r="C146" s="4" t="n"/>
+      <c r="D146" s="4" t="n"/>
+      <c r="E146" s="4" t="n"/>
+      <c r="F146" s="4" t="n"/>
+      <c r="G146" s="4" t="n"/>
+      <c r="H146" s="4" t="n"/>
+      <c r="I146" s="4" t="n"/>
+      <c r="J146" s="4" t="n"/>
+      <c r="K146" s="4" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="19" customHeight="1">
-      <c r="A148" s="3" t="inlineStr">
+    <row r="149" ht="19" customHeight="1">
+      <c r="A149" s="3" t="inlineStr">
         <is>
           <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 58억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B148" s="4" t="n"/>
-      <c r="C148" s="4" t="n"/>
-      <c r="D148" s="4" t="n"/>
-      <c r="E148" s="4" t="n"/>
-      <c r="F148" s="4" t="n"/>
-      <c r="G148" s="4" t="n"/>
-      <c r="H148" s="4" t="n"/>
-      <c r="I148" s="4" t="n"/>
-      <c r="J148" s="4" t="n"/>
-      <c r="K148" s="4" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="20" t="inlineStr">
+      <c r="B149" s="4" t="n"/>
+      <c r="C149" s="4" t="n"/>
+      <c r="D149" s="4" t="n"/>
+      <c r="E149" s="4" t="n"/>
+      <c r="F149" s="4" t="n"/>
+      <c r="G149" s="4" t="n"/>
+      <c r="H149" s="4" t="n"/>
+      <c r="I149" s="4" t="n"/>
+      <c r="J149" s="4" t="n"/>
+      <c r="K149" s="4" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="54">
-    <mergeCell ref="A127:K127"/>
+  <mergeCells count="55">
+    <mergeCell ref="A114:E114"/>
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A143:K143"/>
-    <mergeCell ref="A130:K130"/>
     <mergeCell ref="A39:K39"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A59:K59"/>
     <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A148:K148"/>
-    <mergeCell ref="A142:K142"/>
-    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A138:E138"/>
+    <mergeCell ref="A107:K107"/>
+    <mergeCell ref="A98:K98"/>
     <mergeCell ref="G22:K22"/>
-    <mergeCell ref="G107:K107"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A132:K132"/>
+    <mergeCell ref="A103:K103"/>
     <mergeCell ref="A79:K79"/>
     <mergeCell ref="G48:K48"/>
     <mergeCell ref="A146:K146"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A54:K54"/>
     <mergeCell ref="A65:K65"/>
+    <mergeCell ref="A108:E108"/>
     <mergeCell ref="A128:K128"/>
     <mergeCell ref="G66:K66"/>
-    <mergeCell ref="A137:E137"/>
-    <mergeCell ref="A99:K99"/>
+    <mergeCell ref="A137:K137"/>
+    <mergeCell ref="A133:K133"/>
     <mergeCell ref="A66:E66"/>
     <mergeCell ref="A80:E80"/>
-    <mergeCell ref="G137:K137"/>
-    <mergeCell ref="A136:K136"/>
     <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A105:K105"/>
     <mergeCell ref="A149:K149"/>
-    <mergeCell ref="A145:K145"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A113:E113"/>
-    <mergeCell ref="A104:K104"/>
+    <mergeCell ref="A101:K101"/>
+    <mergeCell ref="G108:K108"/>
+    <mergeCell ref="A113:K113"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A129:K129"/>
     <mergeCell ref="A47:K47"/>
     <mergeCell ref="G80:K80"/>
+    <mergeCell ref="G114:K114"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="G55:K55"/>
+    <mergeCell ref="A150:K150"/>
     <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A106:K106"/>
+    <mergeCell ref="A144:K144"/>
     <mergeCell ref="A97:K97"/>
+    <mergeCell ref="A135:K135"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A131:K131"/>
     <mergeCell ref="A100:K100"/>
-    <mergeCell ref="G113:K113"/>
+    <mergeCell ref="G138:K138"/>
+    <mergeCell ref="A147:K147"/>
     <mergeCell ref="G60:K60"/>
-    <mergeCell ref="A134:K134"/>
     <mergeCell ref="G16:K16"/>
-    <mergeCell ref="A112:K112"/>
-    <mergeCell ref="A102:K102"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="G40:K40"/>
   </mergeCells>

--- a/reports/pdf_weekly_20261030.xlsx
+++ b/reports/pdf_weekly_20261030.xlsx
@@ -916,23 +916,23 @@
       <c r="E12" s="17" t="n"/>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-884660036</v>
+        <v>-846888034</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.99%→0.69%</t>
+          <t>1.18%→0.94%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>24→20</t>
         </is>
       </c>
     </row>
@@ -944,23 +944,23 @@
       <c r="E13" s="17" t="n"/>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-846888034</v>
+        <v>-884660036</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>1.18%→0.94%</t>
+          <t>0.99%→0.69%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>24→20</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
@@ -1541,23 +1541,23 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="B31" s="11" t="n">
         <v>61</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>4247724965</v>
+        <v>2982358620</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>0.91%→2.96%</t>
+          <t>2.22%→3.69%</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>29→90</t>
+          <t>99→160</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
@@ -1585,23 +1585,23 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B32" s="11" t="n">
         <v>61</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2982358620</v>
+        <v>4247724965</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>2.22%→3.69%</t>
+          <t>0.91%→2.96%</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>99→160</t>
+          <t>29→90</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -1629,23 +1629,23 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>엑시콘  (신규)</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="B33" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>2177756110</v>
+        <v>2234451139</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.03%</t>
+          <t>0.95%→2.11%</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>0→50</t>
+          <t>50→100</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
@@ -1673,23 +1673,23 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>엑시콘  (신규)</t>
         </is>
       </c>
       <c r="B34" s="11" t="n">
         <v>50</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>2234451139</v>
+        <v>2177756110</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>0.95%→2.11%</t>
+          <t>0.00%→1.03%</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>50→100</t>
+          <t>0→50</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -3223,23 +3223,23 @@
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>루닛  (신규)</t>
         </is>
       </c>
       <c r="B84" s="11" t="n">
         <v>38</v>
       </c>
       <c r="C84" s="11" t="n">
-        <v>159020196</v>
+        <v>239650154</v>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>2.38%→3.02%</t>
+          <t>0.00%→0.80%</t>
         </is>
       </c>
       <c r="E84" s="13" t="inlineStr">
         <is>
-          <t>178→216</t>
+          <t>0→38</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -3267,23 +3267,23 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>루닛  (신규)</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="B85" s="11" t="n">
         <v>38</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>239650154</v>
+        <v>159020196</v>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.80%</t>
+          <t>2.38%→3.02%</t>
         </is>
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>0→38</t>
+          <t>178→216</t>
         </is>
       </c>
       <c r="G85" s="14" t="inlineStr">
@@ -3420,23 +3420,23 @@
       </c>
       <c r="G88" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H88" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I88" s="15" t="n">
-        <v>-231129110</v>
+        <v>-411106695</v>
       </c>
       <c r="J88" s="16" t="inlineStr">
         <is>
-          <t>2.07%→0.72%</t>
+          <t>3.20%→1.56%</t>
         </is>
       </c>
       <c r="K88" s="13" t="inlineStr">
         <is>
-          <t>29→14</t>
+          <t>32→17</t>
         </is>
       </c>
     </row>
@@ -3464,23 +3464,23 @@
       </c>
       <c r="G89" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H89" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I89" s="15" t="n">
-        <v>-411106695</v>
+        <v>-231129110</v>
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>3.20%→1.56%</t>
+          <t>2.07%→0.72%</t>
         </is>
       </c>
       <c r="K89" s="13" t="inlineStr">
         <is>
-          <t>32→17</t>
+          <t>29→14</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20261030.xlsx
+++ b/reports/pdf_weekly_20261030.xlsx
@@ -59,13 +59,13 @@
       <color rgb="000070C0"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="8">
@@ -171,11 +171,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K150"/>
+  <dimension ref="A1:K149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>주간 변화  ·  2026-10-26 ~ 2026-10-30  (5거래일)  ·  캡처 18/23  ·  대기: TIGER, RISE, RISE, DS, RISE</t>
+          <t>주간 변화  ·  2026-10-26 ~ 2026-10-30  (5거래일)  ·  캡처 17/23  ·  대기: SOL, TIGER, RISE, RISE, DS, RISE</t>
         </is>
       </c>
     </row>
@@ -2010,23 +2010,23 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B44" s="11" t="n">
         <v>85</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>806989840</v>
+        <v>1850925633</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>1.16%→1.71%</t>
+          <t>1.02%→2.23%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>285→370</t>
+          <t>125→210</t>
         </is>
       </c>
       <c r="G44" s="17" t="n"/>
@@ -2038,23 +2038,23 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
         <v>85</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>1850925633</v>
+        <v>806989840</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>1.02%→2.23%</t>
+          <t>1.16%→1.71%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>125→210</t>
+          <t>285→370</t>
         </is>
       </c>
       <c r="G45" s="17" t="n"/>
@@ -3311,23 +3311,23 @@
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>태웅  (신규)</t>
+          <t>제이에스링크</t>
         </is>
       </c>
       <c r="B86" s="11" t="n">
         <v>24</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>238454513</v>
+        <v>193996892</v>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.80%</t>
+          <t>0.32%→1.00%</t>
         </is>
       </c>
       <c r="E86" s="13" t="inlineStr">
         <is>
-          <t>0→24</t>
+          <t>13→37</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -3355,23 +3355,23 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>제이에스링크</t>
+          <t>태웅  (신규)</t>
         </is>
       </c>
       <c r="B87" s="11" t="n">
         <v>24</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>193996892</v>
+        <v>238454513</v>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>0.32%→1.00%</t>
+          <t>0.00%→0.80%</t>
         </is>
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>13→37</t>
+          <t>0→24</t>
         </is>
       </c>
       <c r="G87" s="14" t="inlineStr">
@@ -3420,23 +3420,23 @@
       </c>
       <c r="G88" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H88" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I88" s="15" t="n">
-        <v>-411106695</v>
+        <v>-231129110</v>
       </c>
       <c r="J88" s="16" t="inlineStr">
         <is>
-          <t>3.20%→1.56%</t>
+          <t>2.07%→0.72%</t>
         </is>
       </c>
       <c r="K88" s="13" t="inlineStr">
         <is>
-          <t>32→17</t>
+          <t>29→14</t>
         </is>
       </c>
     </row>
@@ -3464,23 +3464,23 @@
       </c>
       <c r="G89" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H89" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I89" s="15" t="n">
-        <v>-231129110</v>
+        <v>-411106695</v>
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>2.07%→0.72%</t>
+          <t>3.20%→1.56%</t>
         </is>
       </c>
       <c r="K89" s="13" t="inlineStr">
         <is>
-          <t>29→14</t>
+          <t>32→17</t>
         </is>
       </c>
     </row>
@@ -3701,1216 +3701,1208 @@
       </c>
     </row>
     <row r="97" ht="19" customHeight="1">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>■ SOL 코리아메가테크액티브  (신한)      순자산 ≈ 4,113억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="n"/>
-      <c r="C97" s="4" t="n"/>
-      <c r="D97" s="4" t="n"/>
-      <c r="E97" s="4" t="n"/>
-      <c r="F97" s="4" t="n"/>
-      <c r="G97" s="4" t="n"/>
-      <c r="H97" s="4" t="n"/>
-      <c r="I97" s="4" t="n"/>
-      <c r="J97" s="4" t="n"/>
-      <c r="K97" s="4" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="18" t="inlineStr">
+      <c r="A97" s="18" t="inlineStr">
+        <is>
+          <t>■ SOL 코리아메가테크액티브  (신한)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B97" s="19" t="n"/>
+      <c r="C97" s="19" t="n"/>
+      <c r="D97" s="19" t="n"/>
+      <c r="E97" s="19" t="n"/>
+      <c r="F97" s="19" t="n"/>
+      <c r="G97" s="19" t="n"/>
+      <c r="H97" s="19" t="n"/>
+      <c r="I97" s="19" t="n"/>
+      <c r="J97" s="19" t="n"/>
+      <c r="K97" s="19" t="n"/>
+    </row>
+    <row r="99" ht="19" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,254억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="n"/>
+      <c r="C99" s="4" t="n"/>
+      <c r="D99" s="4" t="n"/>
+      <c r="E99" s="4" t="n"/>
+      <c r="F99" s="4" t="n"/>
+      <c r="G99" s="4" t="n"/>
+      <c r="H99" s="4" t="n"/>
+      <c r="I99" s="4" t="n"/>
+      <c r="J99" s="4" t="n"/>
+      <c r="K99" s="4" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="19" customHeight="1">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,254억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="n"/>
-      <c r="C100" s="4" t="n"/>
-      <c r="D100" s="4" t="n"/>
-      <c r="E100" s="4" t="n"/>
-      <c r="F100" s="4" t="n"/>
-      <c r="G100" s="4" t="n"/>
-      <c r="H100" s="4" t="n"/>
-      <c r="I100" s="4" t="n"/>
-      <c r="J100" s="4" t="n"/>
-      <c r="K100" s="4" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="18" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="19" customHeight="1">
-      <c r="A103" s="19" t="inlineStr">
+    <row r="102" ht="19" customHeight="1">
+      <c r="A102" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 코리아테크액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B103" s="20" t="n"/>
-      <c r="C103" s="20" t="n"/>
-      <c r="D103" s="20" t="n"/>
-      <c r="E103" s="20" t="n"/>
-      <c r="F103" s="20" t="n"/>
-      <c r="G103" s="20" t="n"/>
-      <c r="H103" s="20" t="n"/>
-      <c r="I103" s="20" t="n"/>
-      <c r="J103" s="20" t="n"/>
-      <c r="K103" s="20" t="n"/>
-    </row>
-    <row r="105" ht="19" customHeight="1">
-      <c r="A105" s="19" t="inlineStr">
+      <c r="B102" s="19" t="n"/>
+      <c r="C102" s="19" t="n"/>
+      <c r="D102" s="19" t="n"/>
+      <c r="E102" s="19" t="n"/>
+      <c r="F102" s="19" t="n"/>
+      <c r="G102" s="19" t="n"/>
+      <c r="H102" s="19" t="n"/>
+      <c r="I102" s="19" t="n"/>
+      <c r="J102" s="19" t="n"/>
+      <c r="K102" s="19" t="n"/>
+    </row>
+    <row r="104" ht="19" customHeight="1">
+      <c r="A104" s="18" t="inlineStr">
         <is>
           <t>■ RISE 비메모리반도체액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B105" s="20" t="n"/>
-      <c r="C105" s="20" t="n"/>
-      <c r="D105" s="20" t="n"/>
-      <c r="E105" s="20" t="n"/>
-      <c r="F105" s="20" t="n"/>
-      <c r="G105" s="20" t="n"/>
-      <c r="H105" s="20" t="n"/>
-      <c r="I105" s="20" t="n"/>
-      <c r="J105" s="20" t="n"/>
-      <c r="K105" s="20" t="n"/>
-    </row>
-    <row r="107" ht="19" customHeight="1">
-      <c r="A107" s="3" t="inlineStr">
+      <c r="B104" s="19" t="n"/>
+      <c r="C104" s="19" t="n"/>
+      <c r="D104" s="19" t="n"/>
+      <c r="E104" s="19" t="n"/>
+      <c r="F104" s="19" t="n"/>
+      <c r="G104" s="19" t="n"/>
+      <c r="H104" s="19" t="n"/>
+      <c r="I104" s="19" t="n"/>
+      <c r="J104" s="19" t="n"/>
+      <c r="K104" s="19" t="n"/>
+    </row>
+    <row r="106" ht="19" customHeight="1">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 808억      주말 2026-10-30  vs  주초 2026-10-26      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
-      <c r="B107" s="4" t="n"/>
-      <c r="C107" s="4" t="n"/>
-      <c r="D107" s="4" t="n"/>
-      <c r="E107" s="4" t="n"/>
-      <c r="F107" s="4" t="n"/>
-      <c r="G107" s="4" t="n"/>
-      <c r="H107" s="4" t="n"/>
-      <c r="I107" s="4" t="n"/>
-      <c r="J107" s="4" t="n"/>
-      <c r="K107" s="4" t="n"/>
+      <c r="B106" s="4" t="n"/>
+      <c r="C106" s="4" t="n"/>
+      <c r="D106" s="4" t="n"/>
+      <c r="E106" s="4" t="n"/>
+      <c r="F106" s="4" t="n"/>
+      <c r="G106" s="4" t="n"/>
+      <c r="H106" s="4" t="n"/>
+      <c r="I106" s="4" t="n"/>
+      <c r="J106" s="4" t="n"/>
+      <c r="K106" s="4" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="n"/>
+      <c r="C107" s="6" t="n"/>
+      <c r="D107" s="6" t="n"/>
+      <c r="E107" s="6" t="n"/>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="n"/>
+      <c r="I107" s="8" t="n"/>
+      <c r="J107" s="8" t="n"/>
+      <c r="K107" s="8" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="n"/>
-      <c r="C108" s="6" t="n"/>
-      <c r="D108" s="6" t="n"/>
-      <c r="E108" s="6" t="n"/>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H108" s="8" t="n"/>
-      <c r="I108" s="8" t="n"/>
-      <c r="J108" s="8" t="n"/>
-      <c r="K108" s="8" t="n"/>
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K108" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C109" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E109" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G109" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H109" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I109" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J109" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K109" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="C109" s="11" t="n">
+        <v>767188000</v>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>4.24%→5.30%</t>
+        </is>
+      </c>
+      <c r="E109" s="13" t="inlineStr">
+        <is>
+          <t>209→255</t>
+        </is>
+      </c>
+      <c r="G109" s="14" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="H109" s="15" t="n">
+        <v>-1215</v>
+      </c>
+      <c r="I109" s="15" t="n">
+        <v>-772132500</v>
+      </c>
+      <c r="J109" s="16" t="inlineStr">
+        <is>
+          <t>2.95%→1.69%</t>
+        </is>
+      </c>
+      <c r="K109" s="13" t="inlineStr">
+        <is>
+          <t>3,349→2,134</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B110" s="11" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>767188000</v>
+        <v>881826000</v>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>4.24%→5.30%</t>
+          <t>2.92%→4.25%</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>209→255</t>
+          <t>63→85</t>
         </is>
       </c>
       <c r="G110" s="14" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="H110" s="15" t="n">
-        <v>-1215</v>
+        <v>-117</v>
       </c>
       <c r="I110" s="15" t="n">
-        <v>-772132500</v>
+        <v>-748975500</v>
       </c>
       <c r="J110" s="16" t="inlineStr">
         <is>
-          <t>2.95%→1.69%</t>
+          <t>1.99%→0.86%</t>
         </is>
       </c>
       <c r="K110" s="13" t="inlineStr">
         <is>
-          <t>3,349→2,134</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="B111" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="C111" s="11" t="n">
-        <v>881826000</v>
-      </c>
-      <c r="D111" s="12" t="inlineStr">
-        <is>
-          <t>2.92%→4.25%</t>
-        </is>
-      </c>
-      <c r="E111" s="13" t="inlineStr">
-        <is>
-          <t>63→85</t>
-        </is>
-      </c>
-      <c r="G111" s="14" t="inlineStr">
-        <is>
-          <t>삼성에스디에스</t>
-        </is>
-      </c>
-      <c r="H111" s="15" t="n">
-        <v>-117</v>
-      </c>
-      <c r="I111" s="15" t="n">
-        <v>-748975500</v>
-      </c>
-      <c r="J111" s="16" t="inlineStr">
-        <is>
-          <t>1.99%→0.86%</t>
-        </is>
-      </c>
-      <c r="K111" s="13" t="inlineStr">
-        <is>
           <t>225→108</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="19" customHeight="1">
-      <c r="A113" s="3" t="inlineStr">
+    <row r="112" ht="19" customHeight="1">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t>■ KoAct AI인프라액티브  (삼성액티브)      순자산 ≈ 366억      주말 2026-10-30  vs  주초 2026-10-26      매수 11종목  /  매도 11종목</t>
         </is>
       </c>
-      <c r="B113" s="4" t="n"/>
-      <c r="C113" s="4" t="n"/>
-      <c r="D113" s="4" t="n"/>
-      <c r="E113" s="4" t="n"/>
-      <c r="F113" s="4" t="n"/>
-      <c r="G113" s="4" t="n"/>
-      <c r="H113" s="4" t="n"/>
-      <c r="I113" s="4" t="n"/>
-      <c r="J113" s="4" t="n"/>
-      <c r="K113" s="4" t="n"/>
+      <c r="B112" s="4" t="n"/>
+      <c r="C112" s="4" t="n"/>
+      <c r="D112" s="4" t="n"/>
+      <c r="E112" s="4" t="n"/>
+      <c r="F112" s="4" t="n"/>
+      <c r="G112" s="4" t="n"/>
+      <c r="H112" s="4" t="n"/>
+      <c r="I112" s="4" t="n"/>
+      <c r="J112" s="4" t="n"/>
+      <c r="K112" s="4" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="n"/>
+      <c r="C113" s="6" t="n"/>
+      <c r="D113" s="6" t="n"/>
+      <c r="E113" s="6" t="n"/>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="n"/>
+      <c r="I113" s="8" t="n"/>
+      <c r="J113" s="8" t="n"/>
+      <c r="K113" s="8" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="n"/>
-      <c r="C114" s="6" t="n"/>
-      <c r="D114" s="6" t="n"/>
-      <c r="E114" s="6" t="n"/>
-      <c r="G114" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H114" s="8" t="n"/>
-      <c r="I114" s="8" t="n"/>
-      <c r="J114" s="8" t="n"/>
-      <c r="K114" s="8" t="n"/>
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G114" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K114" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C115" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D115" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E115" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G115" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H115" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I115" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J115" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K115" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>샘씨엔에스  (신규)</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="n">
+        <v>1174</v>
+      </c>
+      <c r="C115" s="11" t="n">
+        <v>577889760</v>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.59%</t>
+        </is>
+      </c>
+      <c r="E115" s="13" t="inlineStr">
+        <is>
+          <t>0→1,174</t>
+        </is>
+      </c>
+      <c r="G115" s="14" t="inlineStr">
+        <is>
+          <t>파인엠텍  (편출)</t>
+        </is>
+      </c>
+      <c r="H115" s="15" t="n">
+        <v>-1566</v>
+      </c>
+      <c r="I115" s="15" t="n">
+        <v>-488905200</v>
+      </c>
+      <c r="J115" s="16" t="inlineStr">
+        <is>
+          <t>1.43%→0.00%</t>
+        </is>
+      </c>
+      <c r="K115" s="13" t="inlineStr">
+        <is>
+          <t>1,566→0</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>샘씨엔에스  (신규)</t>
+          <t>한화비전  (신규)</t>
         </is>
       </c>
       <c r="B116" s="11" t="n">
-        <v>1174</v>
+        <v>997</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>577889760</v>
+        <v>1370675600</v>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.59%</t>
+          <t>0.00%→3.78%</t>
         </is>
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>0→1,174</t>
+          <t>0→997</t>
         </is>
       </c>
       <c r="G116" s="14" t="inlineStr">
         <is>
-          <t>파인엠텍  (편출)</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-1566</v>
+        <v>-541</v>
       </c>
       <c r="I116" s="15" t="n">
-        <v>-488905200</v>
+        <v>-691506200</v>
       </c>
       <c r="J116" s="16" t="inlineStr">
         <is>
-          <t>1.43%→0.00%</t>
+          <t>3.36%→1.13%</t>
         </is>
       </c>
       <c r="K116" s="13" t="inlineStr">
         <is>
-          <t>1,566→0</t>
+          <t>861→320</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>한화비전  (신규)</t>
+          <t>인텍플러스  (신규)</t>
         </is>
       </c>
       <c r="B117" s="11" t="n">
-        <v>997</v>
+        <v>324</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>1370675600</v>
+        <v>562464000</v>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>0.00%→3.78%</t>
+          <t>0.00%→1.55%</t>
         </is>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>0→997</t>
+          <t>0→324</t>
         </is>
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>두산퓨얼셀  (편출)</t>
         </is>
       </c>
       <c r="H117" s="15" t="n">
-        <v>-541</v>
+        <v>-513</v>
       </c>
       <c r="I117" s="15" t="n">
-        <v>-691506200</v>
+        <v>-453902400</v>
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>3.36%→1.13%</t>
+          <t>1.33%→0.00%</t>
         </is>
       </c>
       <c r="K117" s="13" t="inlineStr">
         <is>
-          <t>861→320</t>
+          <t>513→0</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스  (신규)</t>
+          <t>ISC  (신규)</t>
         </is>
       </c>
       <c r="B118" s="11" t="n">
-        <v>324</v>
+        <v>165</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>562464000</v>
+        <v>767844000</v>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.55%</t>
+          <t>0.00%→2.12%</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>0→324</t>
+          <t>0→165</t>
         </is>
       </c>
       <c r="G118" s="14" t="inlineStr">
         <is>
-          <t>두산퓨얼셀  (편출)</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="H118" s="15" t="n">
-        <v>-513</v>
+        <v>-473</v>
       </c>
       <c r="I118" s="15" t="n">
-        <v>-453902400</v>
+        <v>-750934800</v>
       </c>
       <c r="J118" s="16" t="inlineStr">
         <is>
-          <t>1.33%→0.00%</t>
+          <t>2.86%→0.50%</t>
         </is>
       </c>
       <c r="K118" s="13" t="inlineStr">
         <is>
-          <t>513→0</t>
+          <t>588→115</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>ISC  (신규)</t>
+          <t>에코프로에이치엔  (신규)</t>
         </is>
       </c>
       <c r="B119" s="11" t="n">
-        <v>165</v>
+        <v>111</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>767844000</v>
+        <v>73038000</v>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.12%</t>
+          <t>0.00%→0.20%</t>
         </is>
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>0→165</t>
+          <t>0→111</t>
         </is>
       </c>
       <c r="G119" s="14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>솔루엠  (편출)</t>
         </is>
       </c>
       <c r="H119" s="15" t="n">
-        <v>-473</v>
+        <v>-325</v>
       </c>
       <c r="I119" s="15" t="n">
-        <v>-750934800</v>
+        <v>-132496000</v>
       </c>
       <c r="J119" s="16" t="inlineStr">
         <is>
-          <t>2.86%→0.50%</t>
+          <t>0.39%→0.00%</t>
         </is>
       </c>
       <c r="K119" s="13" t="inlineStr">
         <is>
-          <t>588→115</t>
+          <t>325→0</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>에코프로에이치엔  (신규)</t>
+          <t>케이씨텍</t>
         </is>
       </c>
       <c r="B120" s="11" t="n">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>73038000</v>
+        <v>163800000</v>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.20%</t>
+          <t>4.99%→5.29%</t>
         </is>
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>0→111</t>
+          <t>644→704</t>
         </is>
       </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
-          <t>솔루엠  (편출)</t>
+          <t>현대건설  (편출)</t>
         </is>
       </c>
       <c r="H120" s="15" t="n">
-        <v>-325</v>
+        <v>-216</v>
       </c>
       <c r="I120" s="15" t="n">
-        <v>-132496000</v>
+        <v>-559440000</v>
       </c>
       <c r="J120" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.00%</t>
+          <t>1.64%→0.00%</t>
         </is>
       </c>
       <c r="K120" s="13" t="inlineStr">
         <is>
-          <t>325→0</t>
+          <t>216→0</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>케이씨텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B121" s="11" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>163800000</v>
+        <v>168565600</v>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>4.99%→5.29%</t>
+          <t>5.55%→6.32%</t>
         </is>
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>644→704</t>
+          <t>391→422</t>
         </is>
       </c>
       <c r="G121" s="14" t="inlineStr">
         <is>
-          <t>현대건설  (편출)</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="H121" s="15" t="n">
-        <v>-216</v>
+        <v>-138</v>
       </c>
       <c r="I121" s="15" t="n">
-        <v>-559440000</v>
+        <v>-896448000</v>
       </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
-          <t>1.64%→0.00%</t>
+          <t>8.61%→6.26%</t>
         </is>
       </c>
       <c r="K121" s="13" t="inlineStr">
         <is>
-          <t>216→0</t>
+          <t>488→350</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B122" s="11" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>168565600</v>
+        <v>118431600</v>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>5.55%→6.32%</t>
+          <t>5.28%→5.77%</t>
         </is>
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>391→422</t>
+          <t>384→407</t>
         </is>
       </c>
       <c r="G122" s="14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="H122" s="15" t="n">
-        <v>-138</v>
+        <v>-30</v>
       </c>
       <c r="I122" s="15" t="n">
-        <v>-896448000</v>
+        <v>-299040000</v>
       </c>
       <c r="J122" s="16" t="inlineStr">
         <is>
-          <t>8.61%→6.26%</t>
+          <t>4.14%→2.80%</t>
         </is>
       </c>
       <c r="K122" s="13" t="inlineStr">
         <is>
-          <t>488→350</t>
+          <t>132→102</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B123" s="11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>118431600</v>
+        <v>331408000</v>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>5.28%→5.77%</t>
+          <t>5.38%→6.47%</t>
         </is>
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>384→407</t>
+          <t>134→156</t>
         </is>
       </c>
       <c r="G123" s="14" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="H123" s="15" t="n">
-        <v>-30</v>
+        <v>-24</v>
       </c>
       <c r="I123" s="15" t="n">
-        <v>-299040000</v>
+        <v>-18480000</v>
       </c>
       <c r="J123" s="16" t="inlineStr">
         <is>
-          <t>4.14%→2.80%</t>
+          <t>2.94%→2.77%</t>
         </is>
       </c>
       <c r="K123" s="13" t="inlineStr">
         <is>
-          <t>132→102</t>
+          <t>1,328→1,304</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B124" s="11" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>331408000</v>
+        <v>341824000</v>
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>5.38%→6.47%</t>
+          <t>8.68%→10.71%</t>
         </is>
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>134→156</t>
+          <t>83→91</t>
         </is>
       </c>
       <c r="G124" s="14" t="inlineStr">
         <is>
-          <t>에스티아이</t>
+          <t>HD현대일렉트릭  (편출)</t>
         </is>
       </c>
       <c r="H124" s="15" t="n">
-        <v>-24</v>
+        <v>-8</v>
       </c>
       <c r="I124" s="15" t="n">
-        <v>-18480000</v>
+        <v>-105280000</v>
       </c>
       <c r="J124" s="16" t="inlineStr">
         <is>
-          <t>2.94%→2.77%</t>
+          <t>0.31%→0.00%</t>
         </is>
       </c>
       <c r="K124" s="13" t="inlineStr">
         <is>
-          <t>1,328→1,304</t>
+          <t>8→0</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B125" s="11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C125" s="11" t="n">
-        <v>341824000</v>
+        <v>108612000</v>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>8.68%→10.71%</t>
+          <t>1.10%→1.50%</t>
         </is>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>83→91</t>
+          <t>12→15</t>
         </is>
       </c>
       <c r="G125" s="14" t="inlineStr">
         <is>
-          <t>HD현대일렉트릭  (편출)</t>
+          <t>두산  (편출)</t>
         </is>
       </c>
       <c r="H125" s="15" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="I125" s="15" t="n">
-        <v>-105280000</v>
+        <v>-188944000</v>
       </c>
       <c r="J125" s="16" t="inlineStr">
         <is>
-          <t>0.31%→0.00%</t>
+          <t>0.55%→0.00%</t>
         </is>
       </c>
       <c r="K125" s="13" t="inlineStr">
         <is>
-          <t>8→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="10" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="B126" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C126" s="11" t="n">
-        <v>108612000</v>
-      </c>
-      <c r="D126" s="12" t="inlineStr">
-        <is>
-          <t>1.10%→1.50%</t>
-        </is>
-      </c>
-      <c r="E126" s="13" t="inlineStr">
-        <is>
-          <t>12→15</t>
-        </is>
-      </c>
-      <c r="G126" s="14" t="inlineStr">
-        <is>
-          <t>두산  (편출)</t>
-        </is>
-      </c>
-      <c r="H126" s="15" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I126" s="15" t="n">
-        <v>-188944000</v>
-      </c>
-      <c r="J126" s="16" t="inlineStr">
-        <is>
-          <t>0.55%→0.00%</t>
-        </is>
-      </c>
-      <c r="K126" s="13" t="inlineStr">
-        <is>
           <t>7→0</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="19" customHeight="1">
-      <c r="A128" s="3" t="inlineStr">
+    <row r="127" ht="19" customHeight="1">
+      <c r="A127" s="3" t="inlineStr">
         <is>
           <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 540억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B128" s="4" t="n"/>
-      <c r="C128" s="4" t="n"/>
-      <c r="D128" s="4" t="n"/>
-      <c r="E128" s="4" t="n"/>
-      <c r="F128" s="4" t="n"/>
-      <c r="G128" s="4" t="n"/>
-      <c r="H128" s="4" t="n"/>
-      <c r="I128" s="4" t="n"/>
-      <c r="J128" s="4" t="n"/>
-      <c r="K128" s="4" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="18" t="inlineStr">
+      <c r="B127" s="4" t="n"/>
+      <c r="C127" s="4" t="n"/>
+      <c r="D127" s="4" t="n"/>
+      <c r="E127" s="4" t="n"/>
+      <c r="F127" s="4" t="n"/>
+      <c r="G127" s="4" t="n"/>
+      <c r="H127" s="4" t="n"/>
+      <c r="I127" s="4" t="n"/>
+      <c r="J127" s="4" t="n"/>
+      <c r="K127" s="4" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="19" customHeight="1">
-      <c r="A131" s="19" t="inlineStr">
+    <row r="130" ht="19" customHeight="1">
+      <c r="A130" s="18" t="inlineStr">
         <is>
           <t>■ RISE 반도체소부장액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B131" s="20" t="n"/>
-      <c r="C131" s="20" t="n"/>
-      <c r="D131" s="20" t="n"/>
-      <c r="E131" s="20" t="n"/>
-      <c r="F131" s="20" t="n"/>
-      <c r="G131" s="20" t="n"/>
-      <c r="H131" s="20" t="n"/>
-      <c r="I131" s="20" t="n"/>
-      <c r="J131" s="20" t="n"/>
-      <c r="K131" s="20" t="n"/>
-    </row>
-    <row r="133" ht="19" customHeight="1">
-      <c r="A133" s="19" t="inlineStr">
+      <c r="B130" s="19" t="n"/>
+      <c r="C130" s="19" t="n"/>
+      <c r="D130" s="19" t="n"/>
+      <c r="E130" s="19" t="n"/>
+      <c r="F130" s="19" t="n"/>
+      <c r="G130" s="19" t="n"/>
+      <c r="H130" s="19" t="n"/>
+      <c r="I130" s="19" t="n"/>
+      <c r="J130" s="19" t="n"/>
+      <c r="K130" s="19" t="n"/>
+    </row>
+    <row r="132" ht="19" customHeight="1">
+      <c r="A132" s="18" t="inlineStr">
         <is>
           <t>■ DS AI반도체액티브  (DS)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B133" s="20" t="n"/>
-      <c r="C133" s="20" t="n"/>
-      <c r="D133" s="20" t="n"/>
-      <c r="E133" s="20" t="n"/>
-      <c r="F133" s="20" t="n"/>
-      <c r="G133" s="20" t="n"/>
-      <c r="H133" s="20" t="n"/>
-      <c r="I133" s="20" t="n"/>
-      <c r="J133" s="20" t="n"/>
-      <c r="K133" s="20" t="n"/>
-    </row>
-    <row r="135" ht="19" customHeight="1">
-      <c r="A135" s="19" t="inlineStr">
+      <c r="B132" s="19" t="n"/>
+      <c r="C132" s="19" t="n"/>
+      <c r="D132" s="19" t="n"/>
+      <c r="E132" s="19" t="n"/>
+      <c r="F132" s="19" t="n"/>
+      <c r="G132" s="19" t="n"/>
+      <c r="H132" s="19" t="n"/>
+      <c r="I132" s="19" t="n"/>
+      <c r="J132" s="19" t="n"/>
+      <c r="K132" s="19" t="n"/>
+    </row>
+    <row r="134" ht="19" customHeight="1">
+      <c r="A134" s="18" t="inlineStr">
         <is>
           <t>■ RISE 2차전지액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B135" s="20" t="n"/>
-      <c r="C135" s="20" t="n"/>
-      <c r="D135" s="20" t="n"/>
-      <c r="E135" s="20" t="n"/>
-      <c r="F135" s="20" t="n"/>
-      <c r="G135" s="20" t="n"/>
-      <c r="H135" s="20" t="n"/>
-      <c r="I135" s="20" t="n"/>
-      <c r="J135" s="20" t="n"/>
-      <c r="K135" s="20" t="n"/>
-    </row>
-    <row r="137" ht="19" customHeight="1">
-      <c r="A137" s="3" t="inlineStr">
+      <c r="B134" s="19" t="n"/>
+      <c r="C134" s="19" t="n"/>
+      <c r="D134" s="19" t="n"/>
+      <c r="E134" s="19" t="n"/>
+      <c r="F134" s="19" t="n"/>
+      <c r="G134" s="19" t="n"/>
+      <c r="H134" s="19" t="n"/>
+      <c r="I134" s="19" t="n"/>
+      <c r="J134" s="19" t="n"/>
+      <c r="K134" s="19" t="n"/>
+    </row>
+    <row r="136" ht="19" customHeight="1">
+      <c r="A136" s="3" t="inlineStr">
         <is>
           <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 281억      주말 2026-10-30  vs  주초 2026-10-26      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
-      <c r="B137" s="4" t="n"/>
-      <c r="C137" s="4" t="n"/>
-      <c r="D137" s="4" t="n"/>
-      <c r="E137" s="4" t="n"/>
-      <c r="F137" s="4" t="n"/>
-      <c r="G137" s="4" t="n"/>
-      <c r="H137" s="4" t="n"/>
-      <c r="I137" s="4" t="n"/>
-      <c r="J137" s="4" t="n"/>
-      <c r="K137" s="4" t="n"/>
+      <c r="B136" s="4" t="n"/>
+      <c r="C136" s="4" t="n"/>
+      <c r="D136" s="4" t="n"/>
+      <c r="E136" s="4" t="n"/>
+      <c r="F136" s="4" t="n"/>
+      <c r="G136" s="4" t="n"/>
+      <c r="H136" s="4" t="n"/>
+      <c r="I136" s="4" t="n"/>
+      <c r="J136" s="4" t="n"/>
+      <c r="K136" s="4" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="n"/>
+      <c r="C137" s="6" t="n"/>
+      <c r="D137" s="6" t="n"/>
+      <c r="E137" s="6" t="n"/>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H137" s="8" t="n"/>
+      <c r="I137" s="8" t="n"/>
+      <c r="J137" s="8" t="n"/>
+      <c r="K137" s="8" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="n"/>
-      <c r="C138" s="6" t="n"/>
-      <c r="D138" s="6" t="n"/>
-      <c r="E138" s="6" t="n"/>
-      <c r="G138" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H138" s="8" t="n"/>
-      <c r="I138" s="8" t="n"/>
-      <c r="J138" s="8" t="n"/>
-      <c r="K138" s="8" t="n"/>
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G138" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H138" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K138" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B139" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C139" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D139" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E139" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G139" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H139" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I139" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J139" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K139" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A139" s="10" t="inlineStr">
+        <is>
+          <t>에코프로에이치엔</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="C139" s="11" t="n">
+        <v>55271980</v>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>0.50%→0.73%</t>
+        </is>
+      </c>
+      <c r="E139" s="13" t="inlineStr">
+        <is>
+          <t>112→154</t>
+        </is>
+      </c>
+      <c r="G139" s="14" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="H139" s="15" t="n">
+        <v>-95</v>
+      </c>
+      <c r="I139" s="15" t="n">
+        <v>-136989951</v>
+      </c>
+      <c r="J139" s="16" t="inlineStr">
+        <is>
+          <t>8.72%→9.20%</t>
+        </is>
+      </c>
+      <c r="K139" s="13" t="inlineStr">
+        <is>
+          <t>1,876→1,781</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>에코프로에이치엔</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="B140" s="11" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>55271980</v>
+        <v>85388770</v>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>0.50%→0.73%</t>
+          <t>6.65%→7.49%</t>
         </is>
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>112→154</t>
+          <t>752→784</t>
         </is>
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>HD현대일렉트릭</t>
         </is>
       </c>
       <c r="H140" s="15" t="n">
-        <v>-95</v>
+        <v>-3</v>
       </c>
       <c r="I140" s="15" t="n">
-        <v>-136989951</v>
+        <v>-74003974</v>
       </c>
       <c r="J140" s="16" t="inlineStr">
         <is>
-          <t>8.72%→9.20%</t>
+          <t>2.17%→1.85%</t>
         </is>
       </c>
       <c r="K140" s="13" t="inlineStr">
         <is>
-          <t>1,876→1,781</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="10" t="inlineStr">
-        <is>
-          <t>한중엔시에스</t>
-        </is>
-      </c>
-      <c r="B141" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="C141" s="11" t="n">
-        <v>85388770</v>
-      </c>
-      <c r="D141" s="12" t="inlineStr">
-        <is>
-          <t>6.65%→7.49%</t>
-        </is>
-      </c>
-      <c r="E141" s="13" t="inlineStr">
-        <is>
-          <t>752→784</t>
-        </is>
-      </c>
-      <c r="G141" s="14" t="inlineStr">
-        <is>
-          <t>HD현대일렉트릭</t>
-        </is>
-      </c>
-      <c r="H141" s="15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I141" s="15" t="n">
-        <v>-74003974</v>
-      </c>
-      <c r="J141" s="16" t="inlineStr">
-        <is>
-          <t>2.17%→1.85%</t>
-        </is>
-      </c>
-      <c r="K141" s="13" t="inlineStr">
-        <is>
           <t>24→21</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="19" customHeight="1">
-      <c r="A143" s="3" t="inlineStr">
+    <row r="142" ht="19" customHeight="1">
+      <c r="A142" s="3" t="inlineStr">
         <is>
           <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 157억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B143" s="4" t="n"/>
-      <c r="C143" s="4" t="n"/>
-      <c r="D143" s="4" t="n"/>
-      <c r="E143" s="4" t="n"/>
-      <c r="F143" s="4" t="n"/>
-      <c r="G143" s="4" t="n"/>
-      <c r="H143" s="4" t="n"/>
-      <c r="I143" s="4" t="n"/>
-      <c r="J143" s="4" t="n"/>
-      <c r="K143" s="4" t="n"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="18" t="inlineStr">
+      <c r="B142" s="4" t="n"/>
+      <c r="C142" s="4" t="n"/>
+      <c r="D142" s="4" t="n"/>
+      <c r="E142" s="4" t="n"/>
+      <c r="F142" s="4" t="n"/>
+      <c r="G142" s="4" t="n"/>
+      <c r="H142" s="4" t="n"/>
+      <c r="I142" s="4" t="n"/>
+      <c r="J142" s="4" t="n"/>
+      <c r="K142" s="4" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="19" customHeight="1">
-      <c r="A146" s="3" t="inlineStr">
+    <row r="145" ht="19" customHeight="1">
+      <c r="A145" s="3" t="inlineStr">
         <is>
           <t>■ KoAct 반도체&amp;2차전지핵심소재액티브  (삼성액티브)      순자산 ≈ 87억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B146" s="4" t="n"/>
-      <c r="C146" s="4" t="n"/>
-      <c r="D146" s="4" t="n"/>
-      <c r="E146" s="4" t="n"/>
-      <c r="F146" s="4" t="n"/>
-      <c r="G146" s="4" t="n"/>
-      <c r="H146" s="4" t="n"/>
-      <c r="I146" s="4" t="n"/>
-      <c r="J146" s="4" t="n"/>
-      <c r="K146" s="4" t="n"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="18" t="inlineStr">
+      <c r="B145" s="4" t="n"/>
+      <c r="C145" s="4" t="n"/>
+      <c r="D145" s="4" t="n"/>
+      <c r="E145" s="4" t="n"/>
+      <c r="F145" s="4" t="n"/>
+      <c r="G145" s="4" t="n"/>
+      <c r="H145" s="4" t="n"/>
+      <c r="I145" s="4" t="n"/>
+      <c r="J145" s="4" t="n"/>
+      <c r="K145" s="4" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="19" customHeight="1">
-      <c r="A149" s="3" t="inlineStr">
+    <row r="148" ht="19" customHeight="1">
+      <c r="A148" s="3" t="inlineStr">
         <is>
           <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 58억      주말 2026-10-30  vs  주초 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B149" s="4" t="n"/>
-      <c r="C149" s="4" t="n"/>
-      <c r="D149" s="4" t="n"/>
-      <c r="E149" s="4" t="n"/>
-      <c r="F149" s="4" t="n"/>
-      <c r="G149" s="4" t="n"/>
-      <c r="H149" s="4" t="n"/>
-      <c r="I149" s="4" t="n"/>
-      <c r="J149" s="4" t="n"/>
-      <c r="K149" s="4" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="18" t="inlineStr">
+      <c r="B148" s="4" t="n"/>
+      <c r="C148" s="4" t="n"/>
+      <c r="D148" s="4" t="n"/>
+      <c r="E148" s="4" t="n"/>
+      <c r="F148" s="4" t="n"/>
+      <c r="G148" s="4" t="n"/>
+      <c r="H148" s="4" t="n"/>
+      <c r="I148" s="4" t="n"/>
+      <c r="J148" s="4" t="n"/>
+      <c r="K148" s="4" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="55">
-    <mergeCell ref="A114:E114"/>
+  <mergeCells count="54">
+    <mergeCell ref="A127:K127"/>
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A143:K143"/>
+    <mergeCell ref="A130:K130"/>
     <mergeCell ref="A39:K39"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A59:K59"/>
     <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A138:E138"/>
-    <mergeCell ref="A107:K107"/>
-    <mergeCell ref="A98:K98"/>
+    <mergeCell ref="A148:K148"/>
+    <mergeCell ref="A142:K142"/>
+    <mergeCell ref="A107:E107"/>
     <mergeCell ref="G22:K22"/>
+    <mergeCell ref="G107:K107"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A103:K103"/>
+    <mergeCell ref="A132:K132"/>
     <mergeCell ref="A79:K79"/>
     <mergeCell ref="G48:K48"/>
     <mergeCell ref="A146:K146"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A54:K54"/>
     <mergeCell ref="A65:K65"/>
-    <mergeCell ref="A108:E108"/>
     <mergeCell ref="A128:K128"/>
     <mergeCell ref="G66:K66"/>
-    <mergeCell ref="A137:K137"/>
-    <mergeCell ref="A133:K133"/>
+    <mergeCell ref="A137:E137"/>
+    <mergeCell ref="A99:K99"/>
     <mergeCell ref="A66:E66"/>
     <mergeCell ref="A80:E80"/>
+    <mergeCell ref="G137:K137"/>
+    <mergeCell ref="A136:K136"/>
     <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A105:K105"/>
     <mergeCell ref="A149:K149"/>
+    <mergeCell ref="A145:K145"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A101:K101"/>
-    <mergeCell ref="G108:K108"/>
-    <mergeCell ref="A113:K113"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A104:K104"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A129:K129"/>
     <mergeCell ref="A47:K47"/>
     <mergeCell ref="G80:K80"/>
-    <mergeCell ref="G114:K114"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="G55:K55"/>
-    <mergeCell ref="A150:K150"/>
     <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A144:K144"/>
+    <mergeCell ref="A106:K106"/>
     <mergeCell ref="A97:K97"/>
-    <mergeCell ref="A135:K135"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A131:K131"/>
     <mergeCell ref="A100:K100"/>
-    <mergeCell ref="G138:K138"/>
-    <mergeCell ref="A147:K147"/>
+    <mergeCell ref="G113:K113"/>
     <mergeCell ref="G60:K60"/>
+    <mergeCell ref="A134:K134"/>
     <mergeCell ref="G16:K16"/>
+    <mergeCell ref="A112:K112"/>
+    <mergeCell ref="A102:K102"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="G40:K40"/>
   </mergeCells>
